--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G3">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G24">

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G24">

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G29">

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G32">

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU40"/>
+  <dimension ref="A1:AU37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G36">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G37">
@@ -6443,495 +6443,6 @@
         <v>0</v>
       </c>
       <c r="AU37" t="inlineStr">
-        <is>
-          <t>2026-09-08 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Nasaf</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Bunyodkor</t>
-        </is>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="U38">
-        <v>0</v>
-      </c>
-      <c r="V38">
-        <v>0</v>
-      </c>
-      <c r="W38">
-        <v>0</v>
-      </c>
-      <c r="X38">
-        <v>0</v>
-      </c>
-      <c r="Y38">
-        <v>0</v>
-      </c>
-      <c r="Z38">
-        <v>0</v>
-      </c>
-      <c r="AA38">
-        <v>0</v>
-      </c>
-      <c r="AB38">
-        <v>0</v>
-      </c>
-      <c r="AC38">
-        <v>0</v>
-      </c>
-      <c r="AD38">
-        <v>0</v>
-      </c>
-      <c r="AE38">
-        <v>0</v>
-      </c>
-      <c r="AF38">
-        <v>0</v>
-      </c>
-      <c r="AG38">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>0</v>
-      </c>
-      <c r="AK38">
-        <v>0</v>
-      </c>
-      <c r="AL38">
-        <v>0</v>
-      </c>
-      <c r="AM38">
-        <v>-1</v>
-      </c>
-      <c r="AN38">
-        <v>-1</v>
-      </c>
-      <c r="AO38">
-        <v>-1</v>
-      </c>
-      <c r="AP38">
-        <v>-1</v>
-      </c>
-      <c r="AQ38">
-        <v>0</v>
-      </c>
-      <c r="AR38">
-        <v>0</v>
-      </c>
-      <c r="AS38">
-        <v>0</v>
-      </c>
-      <c r="AT38">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>2026-09-08 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Željezničar</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Sarajevo</t>
-        </is>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
-        <v>0</v>
-      </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39">
-        <v>0</v>
-      </c>
-      <c r="T39">
-        <v>0</v>
-      </c>
-      <c r="U39">
-        <v>0</v>
-      </c>
-      <c r="V39">
-        <v>0</v>
-      </c>
-      <c r="W39">
-        <v>0</v>
-      </c>
-      <c r="X39">
-        <v>0</v>
-      </c>
-      <c r="Y39">
-        <v>0</v>
-      </c>
-      <c r="Z39">
-        <v>0</v>
-      </c>
-      <c r="AA39">
-        <v>0</v>
-      </c>
-      <c r="AB39">
-        <v>0</v>
-      </c>
-      <c r="AC39">
-        <v>0</v>
-      </c>
-      <c r="AD39">
-        <v>0</v>
-      </c>
-      <c r="AE39">
-        <v>0</v>
-      </c>
-      <c r="AF39">
-        <v>0</v>
-      </c>
-      <c r="AG39">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>0</v>
-      </c>
-      <c r="AK39">
-        <v>0</v>
-      </c>
-      <c r="AL39">
-        <v>0</v>
-      </c>
-      <c r="AM39">
-        <v>-1</v>
-      </c>
-      <c r="AN39">
-        <v>-1</v>
-      </c>
-      <c r="AO39">
-        <v>-1</v>
-      </c>
-      <c r="AP39">
-        <v>-1</v>
-      </c>
-      <c r="AQ39">
-        <v>0</v>
-      </c>
-      <c r="AR39">
-        <v>0</v>
-      </c>
-      <c r="AS39">
-        <v>0</v>
-      </c>
-      <c r="AT39">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>2026-09-08 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>0</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="T40">
-        <v>0</v>
-      </c>
-      <c r="U40">
-        <v>0</v>
-      </c>
-      <c r="V40">
-        <v>0</v>
-      </c>
-      <c r="W40">
-        <v>0</v>
-      </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40">
-        <v>0</v>
-      </c>
-      <c r="Z40">
-        <v>0</v>
-      </c>
-      <c r="AA40">
-        <v>0</v>
-      </c>
-      <c r="AB40">
-        <v>0</v>
-      </c>
-      <c r="AC40">
-        <v>0</v>
-      </c>
-      <c r="AD40">
-        <v>0</v>
-      </c>
-      <c r="AE40">
-        <v>0</v>
-      </c>
-      <c r="AF40">
-        <v>0</v>
-      </c>
-      <c r="AG40">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>0</v>
-      </c>
-      <c r="AK40">
-        <v>0</v>
-      </c>
-      <c r="AL40">
-        <v>0</v>
-      </c>
-      <c r="AM40">
-        <v>-1</v>
-      </c>
-      <c r="AN40">
-        <v>-1</v>
-      </c>
-      <c r="AO40">
-        <v>-1</v>
-      </c>
-      <c r="AP40">
-        <v>-1</v>
-      </c>
-      <c r="AQ40">
-        <v>0</v>
-      </c>
-      <c r="AR40">
-        <v>0</v>
-      </c>
-      <c r="AS40">
-        <v>0</v>
-      </c>
-      <c r="AT40">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
         <is>
           <t>2026-09-08 21:30:00</t>
         </is>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -3402,7 +3402,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N19">

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU37"/>
+  <dimension ref="A1:AU36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,27 +914,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-09-08 11:00:00</t>
+          <t>2026-09-08 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,27 +1077,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-09-08 12:00:00</t>
+          <t>2026-09-08 12:15:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-08 12:15:00</t>
+          <t>2026-09-08 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-09-08 12:30:00</t>
+          <t>2026-09-08 12:55:00</t>
         </is>
       </c>
     </row>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-08 12:55:00</t>
+          <t>2026-09-08 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-08 13:00:00</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G13">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G14">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G15">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00:00</t>
+          <t>2026-09-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-09-08 15:00:00</t>
+          <t>2026-09-08 15:45:00</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G23">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G24">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G25">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-09-08 15:45:00</t>
+          <t>2026-09-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G28">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G29">
@@ -5152,27 +5152,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-09-08 16:00:00</t>
+          <t>2026-09-08 18:00:00</t>
         </is>
       </c>
     </row>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G31">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-08 18:00:00</t>
+          <t>2026-09-08 20:30:00</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G33">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G34">
@@ -5967,27 +5967,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G35">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-09-08 20:30:00</t>
+          <t>2026-09-08 21:00:00</t>
         </is>
       </c>
     </row>
@@ -6130,27 +6130,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G36">
@@ -6280,169 +6280,6 @@
         <v>0</v>
       </c>
       <c r="AU36" t="inlineStr">
-        <is>
-          <t>2026-09-08 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
-        <v>0</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
-      <c r="U37">
-        <v>0</v>
-      </c>
-      <c r="V37">
-        <v>0</v>
-      </c>
-      <c r="W37">
-        <v>0</v>
-      </c>
-      <c r="X37">
-        <v>0</v>
-      </c>
-      <c r="Y37">
-        <v>0</v>
-      </c>
-      <c r="Z37">
-        <v>0</v>
-      </c>
-      <c r="AA37">
-        <v>0</v>
-      </c>
-      <c r="AB37">
-        <v>0</v>
-      </c>
-      <c r="AC37">
-        <v>0</v>
-      </c>
-      <c r="AD37">
-        <v>0</v>
-      </c>
-      <c r="AE37">
-        <v>0</v>
-      </c>
-      <c r="AF37">
-        <v>0</v>
-      </c>
-      <c r="AG37">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>0</v>
-      </c>
-      <c r="AK37">
-        <v>0</v>
-      </c>
-      <c r="AL37">
-        <v>0</v>
-      </c>
-      <c r="AM37">
-        <v>-1</v>
-      </c>
-      <c r="AN37">
-        <v>-1</v>
-      </c>
-      <c r="AO37">
-        <v>-1</v>
-      </c>
-      <c r="AP37">
-        <v>-1</v>
-      </c>
-      <c r="AQ37">
-        <v>0</v>
-      </c>
-      <c r="AR37">
-        <v>0</v>
-      </c>
-      <c r="AS37">
-        <v>0</v>
-      </c>
-      <c r="AT37">
-        <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
         <is>
           <t>2026-09-08 21:30:00</t>
         </is>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.73</v>
+        <v>1.75</v>
       </c>
       <c r="O9">
-        <v>3.55</v>
+        <v>3.96</v>
       </c>
       <c r="P9">
-        <v>2.38</v>
+        <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA9">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB9">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL10">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G23">

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X20">
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
         <v>0</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL29">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU36"/>
+  <dimension ref="A1:AU34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G4">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.47</v>
+        <v>3.97</v>
       </c>
       <c r="O4">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="P4">
-        <v>5.29</v>
+        <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -982,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W4">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-09-08 12:00:00</t>
+          <t>2026-09-08 11:30:00</t>
         </is>
       </c>
     </row>
@@ -1077,27 +1077,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -1157,31 +1157,31 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-09-08 12:15:00</t>
+          <t>2026-09-08 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.97</v>
+        <v>1.75</v>
       </c>
       <c r="O8">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="P8">
-        <v>1.72</v>
+        <v>4.2</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-08 13:00:00</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.75</v>
+        <v>2.73</v>
       </c>
       <c r="O9">
-        <v>3.96</v>
+        <v>3.55</v>
       </c>
       <c r="P9">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q9">
-        <v>2.36</v>
+        <v>3.01</v>
       </c>
       <c r="R9">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="S9">
         <v>1.31</v>
@@ -1797,43 +1797,43 @@
         <v>3.42</v>
       </c>
       <c r="U9">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="V9">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA9">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB9">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AC9">
-        <v>2.49</v>
+        <v>2.68</v>
       </c>
       <c r="AD9">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AE9">
         <v>1.18</v>
       </c>
       <c r="AF9">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AG9">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.73</v>
+        <v>1.48</v>
       </c>
       <c r="O10">
-        <v>3.55</v>
+        <v>4.65</v>
       </c>
       <c r="P10">
+        <v>5.75</v>
+      </c>
+      <c r="Q10">
+        <v>1.85</v>
+      </c>
+      <c r="R10">
+        <v>2.6</v>
+      </c>
+      <c r="S10">
+        <v>1.22</v>
+      </c>
+      <c r="T10">
+        <v>3.66</v>
+      </c>
+      <c r="U10">
+        <v>2.07</v>
+      </c>
+      <c r="V10">
+        <v>1.68</v>
+      </c>
+      <c r="W10">
+        <v>1.16</v>
+      </c>
+      <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>1.1</v>
+      </c>
+      <c r="Z10">
+        <v>5.5</v>
+      </c>
+      <c r="AA10">
+        <v>1.4</v>
+      </c>
+      <c r="AB10">
+        <v>2.88</v>
+      </c>
+      <c r="AC10">
+        <v>2.2</v>
+      </c>
+      <c r="AD10">
+        <v>1.71</v>
+      </c>
+      <c r="AE10">
+        <v>1.3</v>
+      </c>
+      <c r="AF10">
+        <v>1.53</v>
+      </c>
+      <c r="AG10">
         <v>2.38</v>
       </c>
-      <c r="Q10">
-        <v>3.01</v>
-      </c>
-      <c r="R10">
-        <v>2.32</v>
-      </c>
-      <c r="S10">
-        <v>1.31</v>
-      </c>
-      <c r="T10">
-        <v>3.42</v>
-      </c>
-      <c r="U10">
-        <v>2.35</v>
-      </c>
-      <c r="V10">
-        <v>1.55</v>
-      </c>
-      <c r="W10">
-        <v>1.12</v>
-      </c>
-      <c r="X10">
-        <v>1.01</v>
-      </c>
-      <c r="Y10">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.18</v>
       </c>
-      <c r="Z10">
-        <v>4.1</v>
-      </c>
-      <c r="AA10">
-        <v>1.66</v>
-      </c>
-      <c r="AB10">
-        <v>2.2</v>
-      </c>
-      <c r="AC10">
-        <v>2.68</v>
-      </c>
-      <c r="AD10">
-        <v>1.43</v>
-      </c>
-      <c r="AE10">
-        <v>1.18</v>
-      </c>
-      <c r="AF10">
-        <v>1.55</v>
-      </c>
-      <c r="AG10">
-        <v>2.3</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.3</v>
-      </c>
       <c r="AK10">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.48</v>
+        <v>3.21</v>
       </c>
       <c r="O11">
-        <v>4.65</v>
+        <v>2.87</v>
       </c>
       <c r="P11">
-        <v>5.75</v>
+        <v>2.27</v>
       </c>
       <c r="Q11">
-        <v>1.85</v>
+        <v>4.17</v>
       </c>
       <c r="R11">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="S11">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="T11">
-        <v>3.66</v>
+        <v>2.22</v>
       </c>
       <c r="U11">
-        <v>2.07</v>
+        <v>4</v>
       </c>
       <c r="V11">
-        <v>1.68</v>
+        <v>1.2</v>
       </c>
       <c r="W11">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y11">
-        <v>1.1</v>
+        <v>1.56</v>
       </c>
       <c r="Z11">
-        <v>5.5</v>
+        <v>2.21</v>
       </c>
       <c r="AA11">
-        <v>1.4</v>
+        <v>2.84</v>
       </c>
       <c r="AB11">
-        <v>2.88</v>
+        <v>1.41</v>
       </c>
       <c r="AC11">
+        <v>5.56</v>
+      </c>
+      <c r="AD11">
+        <v>1.09</v>
+      </c>
+      <c r="AE11">
+        <v>1.01</v>
+      </c>
+      <c r="AF11">
         <v>2.2</v>
       </c>
-      <c r="AD11">
-        <v>1.71</v>
-      </c>
-      <c r="AE11">
-        <v>1.3</v>
-      </c>
-      <c r="AF11">
-        <v>1.53</v>
-      </c>
       <c r="AG11">
-        <v>2.38</v>
+        <v>1.59</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G13">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00:00</t>
+          <t>2026-09-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00:00</t>
+          <t>2026-09-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-08 15:00:00</t>
+          <t>2026-09-08 15:45:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-09-08 15:00:00</t>
+          <t>2026-09-08 15:45:00</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P19">
-        <v>2.43</v>
+        <v>3.51</v>
       </c>
       <c r="Q19">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="R19">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S19">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U19">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="V19">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z19">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AA19">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AB19">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AC19">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="AD19">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE19">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AG19">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.84</v>
+        <v>2.65</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>3.95</v>
+        <v>2.43</v>
       </c>
       <c r="Q21">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R21">
+        <v>2.17</v>
+      </c>
+      <c r="S21">
+        <v>1.32</v>
+      </c>
+      <c r="T21">
+        <v>3</v>
+      </c>
+      <c r="U21">
+        <v>2.63</v>
+      </c>
+      <c r="V21">
+        <v>1.41</v>
+      </c>
+      <c r="W21">
+        <v>1.07</v>
+      </c>
+      <c r="X21">
+        <v>1.02</v>
+      </c>
+      <c r="Y21">
+        <v>1.23</v>
+      </c>
+      <c r="Z21">
+        <v>3.85</v>
+      </c>
+      <c r="AA21">
+        <v>1.78</v>
+      </c>
+      <c r="AB21">
+        <v>1.97</v>
+      </c>
+      <c r="AC21">
+        <v>2.95</v>
+      </c>
+      <c r="AD21">
+        <v>1.36</v>
+      </c>
+      <c r="AE21">
+        <v>1.12</v>
+      </c>
+      <c r="AF21">
+        <v>1.61</v>
+      </c>
+      <c r="AG21">
         <v>2.18</v>
       </c>
-      <c r="S21">
-        <v>1.37</v>
-      </c>
-      <c r="T21">
-        <v>2.8</v>
-      </c>
-      <c r="U21">
-        <v>2.8</v>
-      </c>
-      <c r="V21">
-        <v>1.37</v>
-      </c>
-      <c r="W21">
-        <v>1.05</v>
-      </c>
-      <c r="X21">
-        <v>1.03</v>
-      </c>
-      <c r="Y21">
-        <v>1.27</v>
-      </c>
-      <c r="Z21">
-        <v>3.45</v>
-      </c>
-      <c r="AA21">
-        <v>1.9</v>
-      </c>
-      <c r="AB21">
-        <v>1.82</v>
-      </c>
-      <c r="AC21">
-        <v>3.3</v>
-      </c>
-      <c r="AD21">
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.3</v>
       </c>
-      <c r="AE21">
-        <v>1.09</v>
-      </c>
-      <c r="AF21">
-        <v>1.76</v>
-      </c>
-      <c r="AG21">
-        <v>1.96</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.29</v>
-      </c>
       <c r="AK21">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G22">
@@ -3891,68 +3891,68 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N22">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,28 +4058,28 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="O23">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="Q23">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R23">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="S23">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="T23">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U23">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
         <v>1.48</v>
@@ -4088,34 +4088,34 @@
         <v>1.09</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>4.35</v>
+        <v>3.9</v>
       </c>
       <c r="AA23">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AB23">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="AC23">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="AD23">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AG23">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-08 15:45:00</t>
+          <t>2026-09-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G24">
@@ -4217,68 +4217,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-08 15:45:00</t>
+          <t>2026-09-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.2</v>
+        <v>1.57</v>
       </c>
       <c r="O25">
-        <v>3.9</v>
+        <v>4.34</v>
       </c>
       <c r="P25">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>3.78</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S25">
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="U25">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V25">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Z25">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AA25">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB25">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="AC25">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="AD25">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AE25">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK25">
-        <v>1.2</v>
+        <v>2.29</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="O26">
-        <v>4.34</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>5</v>
+        <v>1.75</v>
       </c>
       <c r="Q26">
-        <v>2</v>
+        <v>3.78</v>
       </c>
       <c r="R26">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="S26">
         <v>1.25</v>
       </c>
       <c r="T26">
-        <v>3.7</v>
+        <v>3.36</v>
       </c>
       <c r="U26">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V26">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W26">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA26">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AB26">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="AC26">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="AD26">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AE26">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG26">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>2.29</v>
+        <v>1.2</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.2</v>
+        <v>4.09</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P27">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q27">
-        <v>2.75</v>
+        <v>4.35</v>
       </c>
       <c r="R27">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="S27">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T27">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U27">
+        <v>2.4</v>
+      </c>
+      <c r="V27">
+        <v>1.5</v>
+      </c>
+      <c r="W27">
+        <v>1.1</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>1.17</v>
+      </c>
+      <c r="Z27">
+        <v>4.6</v>
+      </c>
+      <c r="AA27">
+        <v>1.61</v>
+      </c>
+      <c r="AB27">
+        <v>2.23</v>
+      </c>
+      <c r="AC27">
         <v>2.5</v>
       </c>
-      <c r="V27">
-        <v>1.48</v>
-      </c>
-      <c r="W27">
-        <v>1.09</v>
-      </c>
-      <c r="X27">
-        <v>1</v>
-      </c>
-      <c r="Y27">
-        <v>1.25</v>
-      </c>
-      <c r="Z27">
-        <v>3.9</v>
-      </c>
-      <c r="AA27">
-        <v>1.82</v>
-      </c>
-      <c r="AB27">
-        <v>2.01</v>
-      </c>
-      <c r="AC27">
-        <v>2.96</v>
-      </c>
       <c r="AD27">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF27">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AG27">
+        <v>2.18</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>2.15</v>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.33</v>
-      </c>
       <c r="AK27">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4826,27 +4826,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-08 16:00:00</t>
+          <t>2026-09-08 18:00:00</t>
         </is>
       </c>
     </row>
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X29">
         <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-09-08 16:00:00</t>
+          <t>2026-09-08 18:00:00</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-09-08 18:00:00</t>
+          <t>2026-09-08 20:30:00</t>
         </is>
       </c>
     </row>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-09-08 18:00:00</t>
+          <t>2026-09-08 20:30:00</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G32">
@@ -5641,27 +5641,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G33">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-09-08 20:30:00</t>
+          <t>2026-09-08 21:00:00</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G34">
@@ -5954,332 +5954,6 @@
         <v>0</v>
       </c>
       <c r="AU34" t="inlineStr">
-        <is>
-          <t>2026-09-08 20:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Željezničar</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Sarajevo</t>
-        </is>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>0</v>
-      </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
-      <c r="AA35">
-        <v>0</v>
-      </c>
-      <c r="AB35">
-        <v>0</v>
-      </c>
-      <c r="AC35">
-        <v>0</v>
-      </c>
-      <c r="AD35">
-        <v>0</v>
-      </c>
-      <c r="AE35">
-        <v>0</v>
-      </c>
-      <c r="AF35">
-        <v>0</v>
-      </c>
-      <c r="AG35">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>0</v>
-      </c>
-      <c r="AK35">
-        <v>0</v>
-      </c>
-      <c r="AL35">
-        <v>0</v>
-      </c>
-      <c r="AM35">
-        <v>-1</v>
-      </c>
-      <c r="AN35">
-        <v>-1</v>
-      </c>
-      <c r="AO35">
-        <v>-1</v>
-      </c>
-      <c r="AP35">
-        <v>-1</v>
-      </c>
-      <c r="AQ35">
-        <v>0</v>
-      </c>
-      <c r="AR35">
-        <v>0</v>
-      </c>
-      <c r="AS35">
-        <v>0</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>2026-09-08 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>0</v>
-      </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
-        <v>0</v>
-      </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
-      <c r="U36">
-        <v>0</v>
-      </c>
-      <c r="V36">
-        <v>0</v>
-      </c>
-      <c r="W36">
-        <v>0</v>
-      </c>
-      <c r="X36">
-        <v>0</v>
-      </c>
-      <c r="Y36">
-        <v>0</v>
-      </c>
-      <c r="Z36">
-        <v>0</v>
-      </c>
-      <c r="AA36">
-        <v>0</v>
-      </c>
-      <c r="AB36">
-        <v>0</v>
-      </c>
-      <c r="AC36">
-        <v>0</v>
-      </c>
-      <c r="AD36">
-        <v>0</v>
-      </c>
-      <c r="AE36">
-        <v>0</v>
-      </c>
-      <c r="AF36">
-        <v>0</v>
-      </c>
-      <c r="AG36">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>0</v>
-      </c>
-      <c r="AK36">
-        <v>0</v>
-      </c>
-      <c r="AL36">
-        <v>0</v>
-      </c>
-      <c r="AM36">
-        <v>-1</v>
-      </c>
-      <c r="AN36">
-        <v>-1</v>
-      </c>
-      <c r="AO36">
-        <v>-1</v>
-      </c>
-      <c r="AP36">
-        <v>-1</v>
-      </c>
-      <c r="AQ36">
-        <v>0</v>
-      </c>
-      <c r="AR36">
-        <v>0</v>
-      </c>
-      <c r="AS36">
-        <v>0</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
         <is>
           <t>2026-09-08 21:30:00</t>
         </is>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.99</v>
+        <v>2.27</v>
       </c>
       <c r="O19">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>3.51</v>
+        <v>2.86</v>
       </c>
       <c r="Q19">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R19">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T19">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19">
+        <v>1.18</v>
+      </c>
+      <c r="Z19">
+        <v>4.5</v>
+      </c>
+      <c r="AA19">
+        <v>1.6</v>
+      </c>
+      <c r="AB19">
+        <v>2.2</v>
+      </c>
+      <c r="AC19">
+        <v>2.55</v>
+      </c>
+      <c r="AD19">
+        <v>1.46</v>
+      </c>
+      <c r="AE19">
+        <v>1.16</v>
+      </c>
+      <c r="AF19">
+        <v>1.52</v>
+      </c>
+      <c r="AG19">
+        <v>2.38</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
         <v>1.27</v>
       </c>
-      <c r="Z19">
-        <v>3.5</v>
-      </c>
-      <c r="AA19">
-        <v>1.91</v>
-      </c>
-      <c r="AB19">
-        <v>1.84</v>
-      </c>
-      <c r="AC19">
-        <v>3.35</v>
-      </c>
-      <c r="AD19">
-        <v>1.29</v>
-      </c>
-      <c r="AE19">
-        <v>1.09</v>
-      </c>
-      <c r="AF19">
-        <v>1.74</v>
-      </c>
-      <c r="AG19">
-        <v>1.98</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.29</v>
-      </c>
       <c r="AK19">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.86</v>
+        <v>2.43</v>
       </c>
       <c r="Q20">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="R20">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="S20">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="T20">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U20">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z20">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="AA20">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AB20">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AC20">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AD20">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AE20">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF20">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AG20">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P21">
-        <v>2.43</v>
+        <v>3.51</v>
       </c>
       <c r="Q21">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="R21">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S21">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T21">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U21">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="V21">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z21">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AA21">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AB21">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AC21">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="AD21">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE21">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF21">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AG21">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.78</v>
+        <v>4.2</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P24">
-        <v>4.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q24">
-        <v>2.29</v>
+        <v>3.78</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S24">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="U24">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="W24">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>5.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA24">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AB24">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="AC24">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="AD24">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AE24">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>2.07</v>
+        <v>1.2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.2</v>
+        <v>1.78</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P26">
-        <v>1.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q26">
-        <v>3.78</v>
+        <v>2.29</v>
       </c>
       <c r="R26">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S26">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T26">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="U26">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="V26">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z26">
-        <v>4.33</v>
+        <v>5.4</v>
       </c>
       <c r="AA26">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AB26">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="AC26">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="AD26">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AE26">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AF26">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG26">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.2</v>
+        <v>2.07</v>
       </c>
       <c r="AL26">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -4740,7 +4740,7 @@
         <v>1.1</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
         <v>1.17</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -1616,40 +1616,40 @@
         <v>1.75</v>
       </c>
       <c r="O8">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="P8">
         <v>4.2</v>
       </c>
       <c r="Q8">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="R8">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S8">
         <v>1.31</v>
       </c>
       <c r="T8">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="U8">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V8">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
         <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA8">
         <v>1.68</v>
@@ -1661,16 +1661,16 @@
         <v>2.49</v>
       </c>
       <c r="AD8">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE8">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
         <v>1.59</v>
       </c>
       <c r="AG8">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
         <v>2.05</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="O9">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P9">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q9">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="R9">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="S9">
         <v>1.31</v>
@@ -1797,16 +1797,16 @@
         <v>3.42</v>
       </c>
       <c r="U9">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="V9">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9">
         <v>1.18</v>
@@ -1824,10 +1824,10 @@
         <v>2.68</v>
       </c>
       <c r="AD9">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE9">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
         <v>1.55</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AK9">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,37 +1939,37 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="O10">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="R10">
         <v>2.6</v>
       </c>
       <c r="S10">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T10">
-        <v>3.66</v>
+        <v>4.8</v>
       </c>
       <c r="U10">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="V10">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="W10">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
         <v>1.1</v>
@@ -1981,13 +1981,13 @@
         <v>1.4</v>
       </c>
       <c r="AB10">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AC10">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AD10">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AE10">
         <v>1.3</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="O18">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
         <v>3.06</v>
       </c>
       <c r="Q18">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="R18">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S18">
         <v>1.28</v>
@@ -3267,31 +3267,31 @@
         <v>2.45</v>
       </c>
       <c r="V18">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z18">
         <v>4.35</v>
       </c>
       <c r="AA18">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB18">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC18">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AD18">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE18">
         <v>1.15</v>
@@ -3300,7 +3300,7 @@
         <v>1.54</v>
       </c>
       <c r="AG18">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK18">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>1.36</v>
       </c>
       <c r="T21">
+        <v>2.8</v>
+      </c>
+      <c r="U21">
         <v>2.85</v>
       </c>
-      <c r="U21">
-        <v>2.8</v>
-      </c>
       <c r="V21">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W21">
         <v>1.05</v>
@@ -3765,19 +3765,19 @@
         <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z21">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AA21">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AB21">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AC21">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AD21">
         <v>1.29</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
         <v>1.76</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="O23">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P23">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q23">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="R23">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W23">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AA23">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AB23">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="AC23">
-        <v>2.96</v>
+        <v>2.58</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>4.2</v>
+        <v>1.58</v>
       </c>
       <c r="O24">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="P24">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>3.78</v>
+        <v>2</v>
       </c>
       <c r="R24">
-        <v>2.32</v>
+        <v>2.64</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T24">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V24">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>4.33</v>
+        <v>5.2</v>
       </c>
       <c r="AA24">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB24">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="AC24">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="AD24">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AE24">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK24">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="O25">
-        <v>4.34</v>
+        <v>4</v>
       </c>
       <c r="P25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="R25">
         <v>2.45</v>
       </c>
       <c r="S25">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T25">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U25">
         <v>2.25</v>
       </c>
       <c r="V25">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W25">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
         <v>1.11</v>
       </c>
       <c r="Z25">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="AA25">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB25">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AC25">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AD25">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE25">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.78</v>
+        <v>2.19</v>
       </c>
       <c r="O26">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q26">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="S26">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.13</v>
+        <v>2.49</v>
       </c>
       <c r="V26">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="W26">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA26">
-        <v>1.51</v>
+        <v>1.82</v>
       </c>
       <c r="AB26">
-        <v>2.34</v>
+        <v>2.01</v>
       </c>
       <c r="AC26">
-        <v>2.4</v>
+        <v>2.96</v>
       </c>
       <c r="AD26">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AE26">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AG26">
-        <v>2.39</v>
+        <v>2.12</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AK26">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>4.09</v>
+        <v>4.45</v>
       </c>
       <c r="O27">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P27">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="Q27">
-        <v>4.35</v>
+        <v>4.68</v>
       </c>
       <c r="R27">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="S27">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U27">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V27">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W27">
         <v>1.1</v>
@@ -4743,31 +4743,31 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA27">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB27">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AC27">
         <v>2.5</v>
       </c>
       <c r="AD27">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AE27">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AG27">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>2.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK27">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL32">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="Q17">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="R17">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="S17">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U17">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z17">
-        <v>3.45</v>
+        <v>4.35</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AB17">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AC17">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="AD17">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE17">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF17">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AG17">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK17">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="O18">
         <v>3.5</v>
       </c>
       <c r="P18">
-        <v>3.06</v>
+        <v>2.86</v>
       </c>
       <c r="Q18">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="R18">
         <v>2.33</v>
       </c>
       <c r="S18">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T18">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U18">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V18">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z18">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="AA18">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB18">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AC18">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="AD18">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE18">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF18">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AG18">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK18">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.86</v>
+        <v>2.43</v>
       </c>
       <c r="Q19">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="R19">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="S19">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="T19">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U19">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W19">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z19">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="AA19">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AB19">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AC19">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AD19">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AE19">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF19">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AG19">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.65</v>
+        <v>1.97</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P20">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="R20">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S20">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U20">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="V20">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z20">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="AA20">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AB20">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AC20">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="AD20">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE20">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AG20">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,31 +3732,31 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="O21">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>3.51</v>
+        <v>3.95</v>
       </c>
       <c r="Q21">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
         <v>2.18</v>
       </c>
       <c r="S21">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T21">
         <v>2.8</v>
       </c>
       <c r="U21">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W21">
         <v>1.05</v>
@@ -3765,13 +3765,13 @@
         <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z21">
         <v>3.45</v>
       </c>
       <c r="AA21">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB21">
         <v>1.82</v>
@@ -3780,16 +3780,16 @@
         <v>3.3</v>
       </c>
       <c r="AD21">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE21">
         <v>1.09</v>
       </c>
       <c r="AF21">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AG21">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="O27">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="P27">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q27">
         <v>4.68</v>
@@ -4749,16 +4749,16 @@
         <v>4.1</v>
       </c>
       <c r="AA27">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB27">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC27">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AD27">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE27">
         <v>1.14</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1942,16 +1942,16 @@
         <v>1.4</v>
       </c>
       <c r="O10">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P10">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q10">
         <v>1.77</v>
       </c>
       <c r="R10">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="S10">
         <v>1.19</v>
@@ -1963,7 +1963,7 @@
         <v>2</v>
       </c>
       <c r="V10">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="W10">
         <v>1.18</v>
@@ -1978,13 +1978,13 @@
         <v>5.5</v>
       </c>
       <c r="AA10">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB10">
         <v>3</v>
       </c>
       <c r="AC10">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AD10">
         <v>1.86</v>
@@ -1996,7 +1996,7 @@
         <v>1.53</v>
       </c>
       <c r="AG10">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,52 +2265,52 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="O12">
         <v>2.7</v>
       </c>
       <c r="P12">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q12">
-        <v>4.2</v>
+        <v>4.31</v>
       </c>
       <c r="R12">
         <v>1.88</v>
       </c>
       <c r="S12">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T12">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="U12">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="V12">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="W12">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
         <v>1.13</v>
       </c>
       <c r="Y12">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z12">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="AA12">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="AB12">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AC12">
-        <v>5.56</v>
+        <v>5.54</v>
       </c>
       <c r="AD12">
         <v>1.1</v>
@@ -2322,7 +2322,7 @@
         <v>2.2</v>
       </c>
       <c r="AG12">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK12">
         <v>1.27</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="O15">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="P15">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="Q15">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
         <v>2.38</v>
@@ -2778,7 +2778,7 @@
         <v>2.13</v>
       </c>
       <c r="V15">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W15">
         <v>1.12</v>
@@ -2805,7 +2805,7 @@
         <v>1.62</v>
       </c>
       <c r="AE15">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF15">
         <v>1.44</v>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -644,55 +644,55 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="O5">
         <v>4.6</v>
       </c>
       <c r="P5">
-        <v>5.29</v>
+        <v>5.2</v>
       </c>
       <c r="Q5">
         <v>2.02</v>
@@ -1619,7 +1619,7 @@
         <v>3.9</v>
       </c>
       <c r="P8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q8">
         <v>2.27</v>
@@ -1631,13 +1631,13 @@
         <v>1.31</v>
       </c>
       <c r="T8">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="U8">
         <v>2.4</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W8">
         <v>1.11</v>
@@ -1661,7 +1661,7 @@
         <v>2.49</v>
       </c>
       <c r="AD8">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE8">
         <v>1.14</v>
@@ -1670,7 +1670,7 @@
         <v>1.59</v>
       </c>
       <c r="AG8">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="O9">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -1800,16 +1800,16 @@
         <v>2.45</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W9">
         <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z9">
         <v>4.1</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="O10">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="P10">
         <v>6.5</v>
@@ -1951,22 +1951,22 @@
         <v>1.77</v>
       </c>
       <c r="R10">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="S10">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T10">
         <v>4.8</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V10">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="W10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X10">
         <v>1.01</v>
@@ -1978,25 +1978,25 @@
         <v>5.5</v>
       </c>
       <c r="AA10">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB10">
         <v>3</v>
       </c>
       <c r="AC10">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AD10">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AE10">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF10">
         <v>1.53</v>
       </c>
       <c r="AG10">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2763,10 +2763,10 @@
         <v>3.6</v>
       </c>
       <c r="Q15">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R15">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="S15">
         <v>1.2</v>
@@ -2778,7 +2778,7 @@
         <v>2.13</v>
       </c>
       <c r="V15">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W15">
         <v>1.12</v>
@@ -2793,7 +2793,7 @@
         <v>5.25</v>
       </c>
       <c r="AA15">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AB15">
         <v>2.43</v>
@@ -2805,13 +2805,13 @@
         <v>1.62</v>
       </c>
       <c r="AE15">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF15">
         <v>1.44</v>
       </c>
       <c r="AG15">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,7 +3083,7 @@
         <v>2.14</v>
       </c>
       <c r="O17">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P17">
         <v>3.05</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -3421,49 +3421,49 @@
         <v>2.17</v>
       </c>
       <c r="S19">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="U19">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="V19">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z19">
-        <v>3.85</v>
+        <v>3.44</v>
       </c>
       <c r="AA19">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AB19">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AC19">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AD19">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE19">
         <v>1.12</v>
       </c>
       <c r="AF19">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG19">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="O20">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q20">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R20">
         <v>2.18</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T20">
         <v>2.8</v>
       </c>
       <c r="U20">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W20">
         <v>1.05</v>
@@ -3602,13 +3602,13 @@
         <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z20">
         <v>3.45</v>
       </c>
       <c r="AA20">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB20">
         <v>1.82</v>
@@ -3617,16 +3617,16 @@
         <v>3.3</v>
       </c>
       <c r="AD20">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
         <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AG20">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK20">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q21">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="R21">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S21">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T21">
         <v>2.8</v>
       </c>
       <c r="U21">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="V21">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W21">
         <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z21">
         <v>3.45</v>
       </c>
       <c r="AA21">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB21">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC21">
         <v>3.3</v>
       </c>
       <c r="AD21">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE21">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG21">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK21">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T23">
         <v>3.3</v>
@@ -4085,7 +4085,7 @@
         <v>1.53</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
         <v>1.01</v>
@@ -4115,7 +4115,7 @@
         <v>1.61</v>
       </c>
       <c r="AG23">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4233,13 +4233,13 @@
         <v>2</v>
       </c>
       <c r="R24">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="S24">
         <v>1.27</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="U24">
         <v>2.25</v>
@@ -4294,7 +4294,7 @@
         <v>1.18</v>
       </c>
       <c r="AK24">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O25">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P25">
         <v>4</v>
@@ -4411,7 +4411,7 @@
         <v>1.62</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
         <v>2.09</v>
@@ -4553,25 +4553,25 @@
         <v>3.5</v>
       </c>
       <c r="P26">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
       </c>
       <c r="R26">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="U26">
         <v>2.49</v>
       </c>
       <c r="V26">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W26">
         <v>1.07</v>
@@ -4737,25 +4737,25 @@
         <v>1.52</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z27">
         <v>4.1</v>
       </c>
       <c r="AA27">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AC27">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="AD27">
         <v>1.43</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O32">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P32">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="Q32">
         <v>2.47</v>
@@ -5540,22 +5540,22 @@
         <v>1.88</v>
       </c>
       <c r="S32">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T32">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="U32">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="V32">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X32">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y32">
         <v>1.51</v>
@@ -5564,16 +5564,16 @@
         <v>2.47</v>
       </c>
       <c r="AA32">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AB32">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AC32">
         <v>4.8</v>
       </c>
       <c r="AD32">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AE32">
         <v>1.02</v>
@@ -5582,7 +5582,7 @@
         <v>2.25</v>
       </c>
       <c r="AG32">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q2">
-        <v>4.01</v>
+        <v>2.35</v>
       </c>
       <c r="R2">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S2">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T2">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="U2">
-        <v>2.36</v>
+        <v>2.84</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>4.25</v>
+        <v>2.85</v>
       </c>
       <c r="AA2">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB2">
-        <v>2.19</v>
+        <v>1.71</v>
       </c>
       <c r="AC2">
-        <v>2.44</v>
+        <v>3.86</v>
       </c>
       <c r="AD2">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AE2">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AG2">
-        <v>2.39</v>
+        <v>1.76</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK2">
-        <v>1.31</v>
+        <v>2</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.35</v>
+        <v>4.01</v>
       </c>
       <c r="R3">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S3">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="T3">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="U3">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z3">
-        <v>2.85</v>
+        <v>4.25</v>
       </c>
       <c r="AA3">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AB3">
-        <v>1.71</v>
+        <v>2.19</v>
       </c>
       <c r="AC3">
-        <v>3.86</v>
+        <v>2.44</v>
       </c>
       <c r="AD3">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>1.95</v>
+        <v>1.51</v>
       </c>
       <c r="AG3">
-        <v>1.76</v>
+        <v>2.39</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK3">
-        <v>2</v>
+        <v>1.31</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -3424,16 +3424,16 @@
         <v>1.35</v>
       </c>
       <c r="T19">
-        <v>2.94</v>
+        <v>3.09</v>
       </c>
       <c r="U19">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
         <v>1</v>
@@ -3442,7 +3442,7 @@
         <v>1.29</v>
       </c>
       <c r="Z19">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="AA19">
         <v>1.83</v>
@@ -3451,19 +3451,19 @@
         <v>1.84</v>
       </c>
       <c r="AC19">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AD19">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
         <v>1.12</v>
       </c>
       <c r="AF19">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG19">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P20">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="Q20">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R20">
         <v>2.18</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK20">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O21">
+        <v>3.35</v>
+      </c>
+      <c r="P21">
         <v>3.3</v>
       </c>
-      <c r="P21">
-        <v>3.25</v>
-      </c>
       <c r="Q21">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="R21">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S21">
         <v>1.36</v>
@@ -3774,7 +3774,7 @@
         <v>1.93</v>
       </c>
       <c r="AB21">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AC21">
         <v>3.3</v>
@@ -3783,13 +3783,13 @@
         <v>1.29</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF21">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG21">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="N27">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="O27">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="P27">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q27">
-        <v>4.68</v>
+        <v>4.72</v>
       </c>
       <c r="R27">
         <v>2.32</v>
@@ -4752,7 +4752,7 @@
         <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AC27">
         <v>2.47</v>
@@ -5534,10 +5534,10 @@
         <v>4.75</v>
       </c>
       <c r="Q32">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="R32">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="S32">
         <v>1.57</v>
@@ -5555,34 +5555,34 @@
         <v>1.01</v>
       </c>
       <c r="X32">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y32">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Z32">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="AA32">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AB32">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AC32">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AD32">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE32">
         <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG32">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AK32">
         <v>1.95</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O32">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P32">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -5546,7 +5546,7 @@
         <v>2.29</v>
       </c>
       <c r="U32">
-        <v>3.52</v>
+        <v>3.9</v>
       </c>
       <c r="V32">
         <v>1.23</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK32">
         <v>1.95</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q34">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.69</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
-        <v>3.69</v>
+        <v>3.25</v>
       </c>
       <c r="P7">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="O10">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q10">
         <v>1.77</v>
@@ -1954,19 +1954,19 @@
         <v>2.6</v>
       </c>
       <c r="S10">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T10">
         <v>4.8</v>
       </c>
       <c r="U10">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="V10">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="W10">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X10">
         <v>1.01</v>
@@ -1978,25 +1978,25 @@
         <v>5.5</v>
       </c>
       <c r="AA10">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB10">
         <v>3</v>
       </c>
       <c r="AC10">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AD10">
         <v>1.73</v>
       </c>
       <c r="AE10">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AF10">
         <v>1.53</v>
       </c>
       <c r="AG10">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK10">
         <v>2.5</v>
@@ -2274,43 +2274,43 @@
         <v>2.35</v>
       </c>
       <c r="Q12">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="R12">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="S12">
         <v>1.58</v>
       </c>
       <c r="T12">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="U12">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="V12">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
         <v>1.13</v>
       </c>
       <c r="Y12">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Z12">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AA12">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="AB12">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AC12">
-        <v>5.54</v>
+        <v>5.53</v>
       </c>
       <c r="AD12">
         <v>1.1</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK12">
         <v>1.27</v>
@@ -2597,58 +2597,58 @@
         <v>4.72</v>
       </c>
       <c r="P14">
-        <v>5.71</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,10 +2763,10 @@
         <v>3.6</v>
       </c>
       <c r="Q15">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="R15">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
         <v>1.2</v>
@@ -2793,10 +2793,10 @@
         <v>5.25</v>
       </c>
       <c r="AA15">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AB15">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AC15">
         <v>2.22</v>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2">
@@ -635,80 +635,80 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>2.35</v>
+        <v>3.7</v>
       </c>
       <c r="R2">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="S2">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="T2">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="U2">
-        <v>2.84</v>
+        <v>2.34</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
+        <v>1.16</v>
+      </c>
+      <c r="Z2">
+        <v>4.2</v>
+      </c>
+      <c r="AA2">
+        <v>1.69</v>
+      </c>
+      <c r="AB2">
+        <v>2.2</v>
+      </c>
+      <c r="AC2">
+        <v>2.63</v>
+      </c>
+      <c r="AD2">
+        <v>1.48</v>
+      </c>
+      <c r="AE2">
+        <v>1.18</v>
+      </c>
+      <c r="AF2">
+        <v>1.52</v>
+      </c>
+      <c r="AG2">
+        <v>2.3</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
+        <v>1.32</v>
+      </c>
+      <c r="AK2">
         <v>1.33</v>
-      </c>
-      <c r="Z2">
-        <v>2.85</v>
-      </c>
-      <c r="AA2">
-        <v>2.1</v>
-      </c>
-      <c r="AB2">
-        <v>1.71</v>
-      </c>
-      <c r="AC2">
-        <v>3.86</v>
-      </c>
-      <c r="AD2">
-        <v>1.21</v>
-      </c>
-      <c r="AE2">
-        <v>1.05</v>
-      </c>
-      <c r="AF2">
-        <v>1.95</v>
-      </c>
-      <c r="AG2">
-        <v>1.76</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.27</v>
-      </c>
-      <c r="AK2">
-        <v>2</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q3">
-        <v>4.01</v>
+        <v>2.32</v>
       </c>
       <c r="R3">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S3">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T3">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="U3">
-        <v>2.36</v>
+        <v>3.04</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="Z3">
-        <v>4.25</v>
+        <v>2.89</v>
       </c>
       <c r="AA3">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="AC3">
-        <v>2.44</v>
+        <v>3.54</v>
       </c>
       <c r="AD3">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AG3">
-        <v>2.39</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AK3">
-        <v>1.31</v>
+        <v>2.02</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="O4">
         <v>3.9</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
         <v>3.8</v>
@@ -1619,10 +1619,10 @@
         <v>3.9</v>
       </c>
       <c r="P8">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q8">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="R8">
         <v>2.5</v>
@@ -1631,22 +1631,22 @@
         <v>1.31</v>
       </c>
       <c r="T8">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="U8">
         <v>2.4</v>
       </c>
       <c r="V8">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W8">
         <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z8">
         <v>4.5</v>
@@ -1661,16 +1661,16 @@
         <v>2.49</v>
       </c>
       <c r="AD8">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE8">
         <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AG8">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="O9">
         <v>3.6</v>
@@ -1785,7 +1785,7 @@
         <v>2.5</v>
       </c>
       <c r="Q9">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="R9">
         <v>2.39</v>
@@ -1797,19 +1797,19 @@
         <v>3.42</v>
       </c>
       <c r="U9">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V9">
         <v>1.51</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
         <v>4.1</v>
@@ -1830,7 +1830,7 @@
         <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG9">
         <v>2.3</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.46</v>
+        <v>1.84</v>
       </c>
       <c r="O14">
-        <v>4.72</v>
+        <v>3.92</v>
       </c>
       <c r="P14">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="Q14">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="R14">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="U14">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V14">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W14">
         <v>1.12</v>
@@ -2624,31 +2624,31 @@
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z14">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA14">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AB14">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AC14">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="AD14">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE14">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF14">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AG14">
-        <v>2.21</v>
+        <v>2.56</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.84</v>
+        <v>1.46</v>
       </c>
       <c r="O15">
-        <v>3.92</v>
+        <v>4.72</v>
       </c>
       <c r="P15">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="Q15">
+        <v>1.87</v>
+      </c>
+      <c r="R15">
+        <v>2.54</v>
+      </c>
+      <c r="S15">
+        <v>1.19</v>
+      </c>
+      <c r="T15">
+        <v>3.78</v>
+      </c>
+      <c r="U15">
         <v>2.15</v>
       </c>
-      <c r="R15">
-        <v>2.5</v>
-      </c>
-      <c r="S15">
-        <v>1.2</v>
-      </c>
-      <c r="T15">
-        <v>3.68</v>
-      </c>
-      <c r="U15">
-        <v>2.13</v>
-      </c>
       <c r="V15">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W15">
         <v>1.12</v>
@@ -2787,31 +2787,31 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z15">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA15">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB15">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AC15">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AD15">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE15">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF15">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AG15">
-        <v>2.56</v>
+        <v>2.21</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK15">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,19 +2920,19 @@
         <v>1.19</v>
       </c>
       <c r="O16">
-        <v>6.4</v>
+        <v>6.65</v>
       </c>
       <c r="P16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q16">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R16">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="S16">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T16">
         <v>3.7</v>
@@ -2944,37 +2944,37 @@
         <v>1.58</v>
       </c>
       <c r="W16">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
         <v>1.13</v>
       </c>
       <c r="Z16">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="AA16">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AB16">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AC16">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AD16">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE16">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF16">
         <v>2.15</v>
       </c>
       <c r="AG16">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK16">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v>3.55</v>
       </c>
       <c r="P17">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="Q17">
         <v>2.65</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="O18">
         <v>3.5</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>3.84</v>
       </c>
       <c r="Q19">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="R19">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S19">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T19">
-        <v>3.09</v>
+        <v>2.8</v>
       </c>
       <c r="U19">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V19">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z19">
-        <v>3.2</v>
+        <v>3.78</v>
       </c>
       <c r="AA19">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB19">
-        <v>1.84</v>
+        <v>2.03</v>
       </c>
       <c r="AC19">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD19">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE19">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG19">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,46 +3569,46 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>3.46</v>
       </c>
       <c r="P20">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="Q20">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="R20">
         <v>2.18</v>
       </c>
       <c r="S20">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
         <v>2.8</v>
       </c>
       <c r="U20">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="V20">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
         <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z20">
         <v>3.45</v>
       </c>
       <c r="AA20">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB20">
         <v>1.82</v>
@@ -3617,32 +3617,32 @@
         <v>3.3</v>
       </c>
       <c r="AD20">
+        <v>1.29</v>
+      </c>
+      <c r="AE20">
+        <v>1.07</v>
+      </c>
+      <c r="AF20">
+        <v>1.74</v>
+      </c>
+      <c r="AG20">
+        <v>1.98</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.3</v>
       </c>
-      <c r="AE20">
-        <v>1.09</v>
-      </c>
-      <c r="AF20">
+      <c r="AK20">
         <v>1.76</v>
-      </c>
-      <c r="AG20">
-        <v>1.96</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.24</v>
-      </c>
-      <c r="AK20">
-        <v>1.95</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,34 +3732,34 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.16</v>
+        <v>3.05</v>
       </c>
       <c r="O21">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="P21">
-        <v>3.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q21">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="R21">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S21">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T21">
-        <v>2.8</v>
+        <v>3.11</v>
       </c>
       <c r="U21">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
         <v>1</v>
@@ -3768,28 +3768,28 @@
         <v>1.28</v>
       </c>
       <c r="Z21">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AA21">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AB21">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AC21">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="AD21">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE21">
         <v>1.12</v>
       </c>
       <c r="AF21">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AG21">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
         <v>3.3</v>
@@ -4085,7 +4085,7 @@
         <v>1.53</v>
       </c>
       <c r="W23">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
         <v>1.01</v>
@@ -4109,13 +4109,13 @@
         <v>1.43</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
         <v>1.61</v>
       </c>
       <c r="AG23">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4221,25 +4221,25 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="P24">
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="R24">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="S24">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="U24">
         <v>2.25</v>
@@ -4248,7 +4248,7 @@
         <v>1.6</v>
       </c>
       <c r="W24">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.79</v>
+        <v>2.19</v>
       </c>
       <c r="O25">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="P25">
-        <v>4</v>
+        <v>2.93</v>
       </c>
       <c r="Q25">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="U25">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="V25">
+        <v>1.44</v>
+      </c>
+      <c r="W25">
+        <v>1.07</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>1.25</v>
+      </c>
+      <c r="Z25">
+        <v>3.9</v>
+      </c>
+      <c r="AA25">
+        <v>1.82</v>
+      </c>
+      <c r="AB25">
+        <v>2.01</v>
+      </c>
+      <c r="AC25">
+        <v>2.96</v>
+      </c>
+      <c r="AD25">
+        <v>1.35</v>
+      </c>
+      <c r="AE25">
+        <v>1.1</v>
+      </c>
+      <c r="AF25">
         <v>1.62</v>
       </c>
-      <c r="W25">
-        <v>1.16</v>
-      </c>
-      <c r="X25">
-        <v>1.03</v>
-      </c>
-      <c r="Y25">
-        <v>1.11</v>
-      </c>
-      <c r="Z25">
-        <v>4.9</v>
-      </c>
-      <c r="AA25">
-        <v>1.5</v>
-      </c>
-      <c r="AB25">
-        <v>2.36</v>
-      </c>
-      <c r="AC25">
-        <v>2.36</v>
-      </c>
-      <c r="AD25">
-        <v>1.66</v>
-      </c>
-      <c r="AE25">
-        <v>1.22</v>
-      </c>
-      <c r="AF25">
-        <v>1.53</v>
-      </c>
       <c r="AG25">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AK25">
-        <v>2.09</v>
+        <v>1.65</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="O26">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P26">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="Q26">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="R26">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="T26">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="U26">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="V26">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="Z26">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="AA26">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AB26">
-        <v>2.01</v>
+        <v>2.36</v>
       </c>
       <c r="AC26">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="AD26">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG26">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.62</v>
+        <v>2.09</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>4.45</v>
+        <v>4.29</v>
       </c>
       <c r="O27">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P27">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q27">
-        <v>4.72</v>
+        <v>4.75</v>
       </c>
       <c r="R27">
         <v>2.32</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T27">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="U27">
         <v>2.38</v>
@@ -4737,37 +4737,37 @@
         <v>1.52</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA27">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB27">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AC27">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AD27">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE27">
         <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5540,10 +5540,10 @@
         <v>1.95</v>
       </c>
       <c r="S32">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T32">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="U32">
         <v>3.9</v>
@@ -5552,16 +5552,16 @@
         <v>1.23</v>
       </c>
       <c r="W32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
         <v>1.07</v>
       </c>
       <c r="Y32">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Z32">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="AA32">
         <v>2.46</v>
@@ -5573,10 +5573,10 @@
         <v>5.4</v>
       </c>
       <c r="AD32">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE32">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF32">
         <v>2.3</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK32">
         <v>1.95</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P34">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU34"/>
+  <dimension ref="A1:AU35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,19 +644,19 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>3.7</v>
+        <v>4.06</v>
       </c>
       <c r="R2">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="S2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T2">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U2">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="V2">
         <v>1.51</v>
@@ -668,22 +668,22 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA2">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB2">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AC2">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AD2">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE2">
         <v>1.18</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK2">
         <v>1.33</v>
@@ -813,7 +813,7 @@
         <v>2.08</v>
       </c>
       <c r="S3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
         <v>2.62</v>
@@ -822,10 +822,10 @@
         <v>3.04</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK3">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -914,27 +914,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.95</v>
+        <v>1.85</v>
       </c>
       <c r="O4">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="Q4">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="R4">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U4">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V4">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z4">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AA4">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB4">
         <v>2.5</v>
       </c>
       <c r="AC4">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="AD4">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AE4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG4">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-09-08 11:30:00</t>
+          <t>2026-09-08 09:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.46</v>
+        <v>3.95</v>
       </c>
       <c r="O5">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
+        <v>1.7</v>
+      </c>
+      <c r="Q5">
+        <v>3.8</v>
+      </c>
+      <c r="R5">
+        <v>2.5</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>2.08</v>
+      </c>
+      <c r="V5">
+        <v>1.63</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>1.1</v>
+      </c>
+      <c r="Z5">
         <v>5.2</v>
       </c>
-      <c r="Q5">
-        <v>2.02</v>
-      </c>
-      <c r="R5">
-        <v>2.65</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>2</v>
-      </c>
-      <c r="V5">
-        <v>1.68</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>1.08</v>
-      </c>
-      <c r="Z5">
-        <v>5.75</v>
-      </c>
       <c r="AA5">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AB5">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AC5">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AD5">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AE5">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF5">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AG5">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>2.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-09-08 12:00:00</t>
+          <t>2026-09-08 11:30:00</t>
         </is>
       </c>
     </row>
@@ -1240,27 +1240,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1308,10 +1308,10 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -1320,31 +1320,31 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-08 12:30:00</t>
+          <t>2026-09-08 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-09-08 12:55:00</t>
+          <t>2026-09-08 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="O8">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q8">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 12:55:00</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,65 +1776,65 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="O9">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P9">
+        <v>4.2</v>
+      </c>
+      <c r="Q9">
+        <v>2.26</v>
+      </c>
+      <c r="R9">
         <v>2.5</v>
-      </c>
-      <c r="Q9">
-        <v>3.19</v>
-      </c>
-      <c r="R9">
-        <v>2.39</v>
       </c>
       <c r="S9">
         <v>1.31</v>
       </c>
       <c r="T9">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="U9">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="V9">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA9">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB9">
+        <v>2.32</v>
+      </c>
+      <c r="AC9">
+        <v>2.49</v>
+      </c>
+      <c r="AD9">
+        <v>1.48</v>
+      </c>
+      <c r="AE9">
+        <v>1.14</v>
+      </c>
+      <c r="AF9">
+        <v>1.64</v>
+      </c>
+      <c r="AG9">
         <v>2.2</v>
       </c>
-      <c r="AC9">
-        <v>2.68</v>
-      </c>
-      <c r="AD9">
-        <v>1.42</v>
-      </c>
-      <c r="AE9">
-        <v>1.13</v>
-      </c>
-      <c r="AF9">
-        <v>1.53</v>
-      </c>
-      <c r="AG9">
-        <v>2.3</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.53</v>
+        <v>2.63</v>
       </c>
       <c r="O10">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="P10">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q10">
-        <v>1.77</v>
+        <v>3.19</v>
       </c>
       <c r="R10">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="S10">
+        <v>1.31</v>
+      </c>
+      <c r="T10">
+        <v>3.42</v>
+      </c>
+      <c r="U10">
+        <v>2.46</v>
+      </c>
+      <c r="V10">
+        <v>1.51</v>
+      </c>
+      <c r="W10">
+        <v>1.12</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
         <v>1.18</v>
       </c>
-      <c r="T10">
-        <v>4.8</v>
-      </c>
-      <c r="U10">
-        <v>1.92</v>
-      </c>
-      <c r="V10">
-        <v>1.83</v>
-      </c>
-      <c r="W10">
-        <v>1.2</v>
-      </c>
-      <c r="X10">
-        <v>1.01</v>
-      </c>
-      <c r="Y10">
-        <v>1.1</v>
-      </c>
       <c r="Z10">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA10">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="AB10">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AC10">
-        <v>1.81</v>
+        <v>2.68</v>
       </c>
       <c r="AD10">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AE10">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
         <v>1.53</v>
       </c>
       <c r="AG10">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="AK10">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00:00</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-08 15:00:00</t>
+          <t>2026-09-08 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.46</v>
+        <v>1.84</v>
       </c>
       <c r="O15">
-        <v>4.72</v>
+        <v>3.92</v>
       </c>
       <c r="P15">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="Q15">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="R15">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="U15">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V15">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W15">
         <v>1.12</v>
@@ -2787,31 +2787,31 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z15">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA15">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AB15">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AC15">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="AD15">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE15">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF15">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AG15">
-        <v>2.21</v>
+        <v>2.56</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
+        <v>1.46</v>
+      </c>
+      <c r="O16">
+        <v>4.72</v>
+      </c>
+      <c r="P16">
+        <v>6</v>
+      </c>
+      <c r="Q16">
+        <v>1.87</v>
+      </c>
+      <c r="R16">
+        <v>2.54</v>
+      </c>
+      <c r="S16">
         <v>1.19</v>
       </c>
-      <c r="O16">
-        <v>6.65</v>
-      </c>
-      <c r="P16">
-        <v>11</v>
-      </c>
-      <c r="Q16">
-        <v>1.54</v>
-      </c>
-      <c r="R16">
-        <v>2.93</v>
-      </c>
-      <c r="S16">
-        <v>1.22</v>
-      </c>
       <c r="T16">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="U16">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="V16">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W16">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>4.64</v>
+        <v>5.2</v>
       </c>
       <c r="AA16">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AB16">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AC16">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AD16">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AE16">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF16">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="AG16">
-        <v>1.65</v>
+        <v>2.21</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK16">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-08 15:45:00</t>
+          <t>2026-09-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.14</v>
+        <v>1.19</v>
       </c>
       <c r="O17">
-        <v>3.55</v>
+        <v>6.65</v>
       </c>
       <c r="P17">
-        <v>3.06</v>
+        <v>11</v>
       </c>
       <c r="Q17">
-        <v>2.65</v>
+        <v>1.54</v>
       </c>
       <c r="R17">
-        <v>2.33</v>
+        <v>2.93</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="U17">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
+        <v>1.13</v>
+      </c>
+      <c r="Z17">
+        <v>4.64</v>
+      </c>
+      <c r="AA17">
+        <v>1.52</v>
+      </c>
+      <c r="AB17">
+        <v>2.44</v>
+      </c>
+      <c r="AC17">
+        <v>2.29</v>
+      </c>
+      <c r="AD17">
+        <v>1.55</v>
+      </c>
+      <c r="AE17">
         <v>1.19</v>
       </c>
-      <c r="Z17">
-        <v>4.35</v>
-      </c>
-      <c r="AA17">
-        <v>1.67</v>
-      </c>
-      <c r="AB17">
-        <v>2.12</v>
-      </c>
-      <c r="AC17">
-        <v>2.65</v>
-      </c>
-      <c r="AD17">
-        <v>1.44</v>
-      </c>
-      <c r="AE17">
-        <v>1.15</v>
-      </c>
       <c r="AF17">
-        <v>1.54</v>
+        <v>2.15</v>
       </c>
       <c r="AG17">
-        <v>2.32</v>
+        <v>1.65</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AK17">
-        <v>1.65</v>
+        <v>4.4</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P18">
-        <v>2.86</v>
+        <v>3.06</v>
       </c>
       <c r="Q18">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="R18">
         <v>2.33</v>
       </c>
       <c r="S18">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T18">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U18">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z18">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="AA18">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB18">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AC18">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="AD18">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE18">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF18">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AG18">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK18">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="O19">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>3.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q19">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="R19">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="S19">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="T19">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="V19">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>3.78</v>
+        <v>4.5</v>
       </c>
       <c r="AA19">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AB19">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AC19">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="AD19">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF19">
-        <v>1.76</v>
+        <v>1.52</v>
       </c>
       <c r="AG19">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK19">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="O20">
-        <v>3.46</v>
+        <v>3.74</v>
       </c>
       <c r="P20">
-        <v>3.25</v>
+        <v>3.84</v>
       </c>
       <c r="Q20">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="R20">
         <v>2.18</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T20">
         <v>2.8</v>
       </c>
       <c r="U20">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W20">
         <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z20">
-        <v>3.45</v>
+        <v>3.78</v>
       </c>
       <c r="AA20">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB20">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AC20">
         <v>3.3</v>
       </c>
       <c r="AD20">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AG20">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,34 +3732,34 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.05</v>
+        <v>2.12</v>
       </c>
       <c r="O21">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="P21">
-        <v>2.21</v>
+        <v>3.25</v>
       </c>
       <c r="Q21">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="R21">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S21">
+        <v>1.36</v>
+      </c>
+      <c r="T21">
+        <v>2.8</v>
+      </c>
+      <c r="U21">
+        <v>2.77</v>
+      </c>
+      <c r="V21">
         <v>1.35</v>
       </c>
-      <c r="T21">
-        <v>3.11</v>
-      </c>
-      <c r="U21">
-        <v>2.75</v>
-      </c>
-      <c r="V21">
-        <v>1.43</v>
-      </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
         <v>1</v>
@@ -3768,28 +3768,28 @@
         <v>1.28</v>
       </c>
       <c r="Z21">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AA21">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AB21">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AC21">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="AD21">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE21">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AG21">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G22">
@@ -3891,68 +3891,68 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G23">
@@ -4054,68 +4054,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N23">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-08 16:00:00</t>
+          <t>2026-09-08 15:45:00</t>
         </is>
       </c>
     </row>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="O24">
-        <v>4.26</v>
+        <v>3.9</v>
       </c>
       <c r="P24">
-        <v>5</v>
+        <v>1.75</v>
       </c>
       <c r="Q24">
-        <v>2.09</v>
+        <v>4</v>
       </c>
       <c r="R24">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T24">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W24">
         <v>1.13</v>
@@ -4254,47 +4254,47 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA24">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="AC24">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="AD24">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AE24">
+        <v>1.14</v>
+      </c>
+      <c r="AF24">
+        <v>1.61</v>
+      </c>
+      <c r="AG24">
+        <v>2.16</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>1.27</v>
+      </c>
+      <c r="AK24">
         <v>1.22</v>
-      </c>
-      <c r="AF24">
-        <v>1.6</v>
-      </c>
-      <c r="AG24">
-        <v>2.3</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.17</v>
-      </c>
-      <c r="AK24">
-        <v>2.29</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.19</v>
+        <v>1.6</v>
       </c>
       <c r="O25">
-        <v>3.45</v>
+        <v>4.26</v>
       </c>
       <c r="P25">
-        <v>2.93</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>2.75</v>
+        <v>2.09</v>
       </c>
       <c r="R25">
+        <v>2.43</v>
+      </c>
+      <c r="S25">
+        <v>1.25</v>
+      </c>
+      <c r="T25">
+        <v>3.66</v>
+      </c>
+      <c r="U25">
         <v>2.25</v>
       </c>
-      <c r="S25">
-        <v>1.3</v>
-      </c>
-      <c r="T25">
-        <v>3.21</v>
-      </c>
-      <c r="U25">
-        <v>2.49</v>
-      </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z25">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="AA25">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AB25">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="AC25">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="AD25">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AE25">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="O26">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="P26">
-        <v>4</v>
+        <v>2.93</v>
       </c>
       <c r="Q26">
-        <v>2.26</v>
+        <v>2.75</v>
       </c>
       <c r="R26">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="U26">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="V26">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA26">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AB26">
-        <v>2.36</v>
+        <v>2.01</v>
       </c>
       <c r="AC26">
-        <v>2.36</v>
+        <v>2.96</v>
       </c>
       <c r="AD26">
+        <v>1.35</v>
+      </c>
+      <c r="AE26">
+        <v>1.1</v>
+      </c>
+      <c r="AF26">
         <v>1.62</v>
       </c>
-      <c r="AE26">
-        <v>1.22</v>
-      </c>
-      <c r="AF26">
-        <v>1.53</v>
-      </c>
       <c r="AG26">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AK26">
-        <v>2.09</v>
+        <v>1.65</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>4.29</v>
+        <v>1.8</v>
       </c>
       <c r="O27">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P27">
-        <v>1.72</v>
+        <v>4</v>
       </c>
       <c r="Q27">
+        <v>2.26</v>
+      </c>
+      <c r="R27">
+        <v>2.42</v>
+      </c>
+      <c r="S27">
+        <v>1.2</v>
+      </c>
+      <c r="T27">
+        <v>4</v>
+      </c>
+      <c r="U27">
+        <v>2.25</v>
+      </c>
+      <c r="V27">
+        <v>1.61</v>
+      </c>
+      <c r="W27">
+        <v>1.13</v>
+      </c>
+      <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>1.11</v>
+      </c>
+      <c r="Z27">
         <v>4.75</v>
       </c>
-      <c r="R27">
-        <v>2.32</v>
-      </c>
-      <c r="S27">
-        <v>1.27</v>
-      </c>
-      <c r="T27">
-        <v>3.22</v>
-      </c>
-      <c r="U27">
-        <v>2.38</v>
-      </c>
-      <c r="V27">
-        <v>1.52</v>
-      </c>
-      <c r="W27">
-        <v>1.1</v>
-      </c>
-      <c r="X27">
-        <v>1.02</v>
-      </c>
-      <c r="Y27">
+      <c r="AA27">
+        <v>1.5</v>
+      </c>
+      <c r="AB27">
+        <v>2.36</v>
+      </c>
+      <c r="AC27">
+        <v>2.36</v>
+      </c>
+      <c r="AD27">
+        <v>1.62</v>
+      </c>
+      <c r="AE27">
         <v>1.22</v>
       </c>
-      <c r="Z27">
-        <v>4.05</v>
-      </c>
-      <c r="AA27">
-        <v>1.63</v>
-      </c>
-      <c r="AB27">
-        <v>2.18</v>
-      </c>
-      <c r="AC27">
-        <v>2.5</v>
-      </c>
-      <c r="AD27">
-        <v>1.42</v>
-      </c>
-      <c r="AE27">
-        <v>1.14</v>
-      </c>
       <c r="AF27">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG27">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.19</v>
+        <v>2.09</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4826,27 +4826,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.21</v>
+        <v>4.29</v>
       </c>
       <c r="O28">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="P28">
-        <v>3.1</v>
+        <v>1.72</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-08 18:00:00</t>
+          <t>2026-09-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-09-08 20:30:00</t>
+          <t>2026-09-08 18:00:00</t>
         </is>
       </c>
     </row>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O31">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.75</v>
+        <v>2.39</v>
       </c>
       <c r="O32">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P32">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q32">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5641,27 +5641,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-09-08 21:00:00</t>
+          <t>2026-09-08 20:30:00</t>
         </is>
       </c>
     </row>
@@ -5804,156 +5804,319 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Željezničar</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sarajevo</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-1</v>
+      </c>
+      <c r="AN34">
+        <v>-1</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>-1</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Juventude</t>
         </is>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34" t="inlineStr">
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N34">
-        <v>2.1</v>
-      </c>
-      <c r="O34">
-        <v>2.7</v>
-      </c>
-      <c r="P34">
-        <v>3.8</v>
-      </c>
-      <c r="Q34">
-        <v>2.77</v>
-      </c>
-      <c r="R34">
-        <v>1.87</v>
-      </c>
-      <c r="S34">
-        <v>1.5</v>
-      </c>
-      <c r="T34">
-        <v>2.19</v>
-      </c>
-      <c r="U34">
-        <v>3.75</v>
-      </c>
-      <c r="V34">
-        <v>1.22</v>
-      </c>
-      <c r="W34">
-        <v>1.02</v>
-      </c>
-      <c r="X34">
-        <v>1.11</v>
-      </c>
-      <c r="Y34">
+      <c r="N35">
+        <v>2.05</v>
+      </c>
+      <c r="O35">
+        <v>2.9</v>
+      </c>
+      <c r="P35">
+        <v>3.5</v>
+      </c>
+      <c r="Q35">
+        <v>2.88</v>
+      </c>
+      <c r="R35">
+        <v>1.73</v>
+      </c>
+      <c r="S35">
+        <v>1.67</v>
+      </c>
+      <c r="T35">
+        <v>2.11</v>
+      </c>
+      <c r="U35">
+        <v>4.1</v>
+      </c>
+      <c r="V35">
+        <v>1.2</v>
+      </c>
+      <c r="W35">
+        <v>1.04</v>
+      </c>
+      <c r="X35">
+        <v>1.14</v>
+      </c>
+      <c r="Y35">
         <v>1.55</v>
       </c>
-      <c r="Z34">
-        <v>2.34</v>
-      </c>
-      <c r="AA34">
-        <v>2.83</v>
-      </c>
-      <c r="AB34">
-        <v>1.38</v>
-      </c>
-      <c r="AC34">
+      <c r="Z35">
+        <v>2.44</v>
+      </c>
+      <c r="AA35">
+        <v>2.52</v>
+      </c>
+      <c r="AB35">
+        <v>1.43</v>
+      </c>
+      <c r="AC35">
         <v>5.41</v>
       </c>
-      <c r="AD34">
-        <v>1.15</v>
-      </c>
-      <c r="AE34">
+      <c r="AD35">
+        <v>1.12</v>
+      </c>
+      <c r="AE35">
         <v>1.04</v>
       </c>
-      <c r="AF34">
-        <v>2.3</v>
-      </c>
-      <c r="AG34">
-        <v>1.56</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.49</v>
-      </c>
-      <c r="AK34">
-        <v>1.62</v>
-      </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>-1</v>
-      </c>
-      <c r="AN34">
-        <v>-1</v>
-      </c>
-      <c r="AO34">
-        <v>-1</v>
-      </c>
-      <c r="AP34">
-        <v>-1</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
+      <c r="AF35">
+        <v>2.25</v>
+      </c>
+      <c r="AG35">
+        <v>1.59</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.41</v>
+      </c>
+      <c r="AK35">
+        <v>1.68</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>-1</v>
+      </c>
+      <c r="AN35">
+        <v>-1</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>-1</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
         <is>
           <t>2026-09-08 21:30:00</t>
         </is>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU35"/>
+  <dimension ref="A1:AU34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q2">
-        <v>4.06</v>
+        <v>2.32</v>
       </c>
       <c r="R2">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="U2">
-        <v>2.44</v>
+        <v>3.04</v>
       </c>
       <c r="V2">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="Z2">
-        <v>4.25</v>
+        <v>2.89</v>
       </c>
       <c r="AA2">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB2">
-        <v>2.18</v>
+        <v>1.69</v>
       </c>
       <c r="AC2">
-        <v>2.45</v>
+        <v>3.88</v>
       </c>
       <c r="AD2">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="AG2">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK2">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.32</v>
+        <v>3.85</v>
       </c>
       <c r="R3">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="S3">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="U3">
-        <v>3.04</v>
+        <v>2.33</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="Z3">
-        <v>2.89</v>
+        <v>4.67</v>
       </c>
       <c r="AA3">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AB3">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AC3">
-        <v>3.54</v>
+        <v>2.63</v>
       </c>
       <c r="AD3">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF3">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AG3">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="O4">
         <v>4.2</v>
       </c>
       <c r="P4">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="O5">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P5">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="Q5">
-        <v>3.8</v>
+        <v>4.24</v>
       </c>
       <c r="R5">
         <v>2.5</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U5">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V5">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB5">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC5">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD5">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE5">
         <v>1.21</v>
       </c>
       <c r="AF5">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AG5">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="O6">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P6">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="Q6">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="R6">
         <v>2.65</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V6">
         <v>1.68</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z6">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA6">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB6">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AC6">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AD6">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AE6">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF6">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AG6">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.75</v>
+        <v>2.72</v>
       </c>
       <c r="O9">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q9">
-        <v>2.26</v>
+        <v>3.01</v>
       </c>
       <c r="R9">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T9">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="U9">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V9">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
         <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
         <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AA9">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB9">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AC9">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="AD9">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AG9">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="AK9">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="P10">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q10">
-        <v>3.19</v>
+        <v>2.33</v>
       </c>
       <c r="R10">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="S10">
         <v>1.31</v>
       </c>
       <c r="T10">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="U10">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="V10">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z10">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA10">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB10">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC10">
-        <v>2.68</v>
+        <v>2.51</v>
       </c>
       <c r="AD10">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AG10">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="O11">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P11">
         <v>4.7</v>
       </c>
       <c r="Q11">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R11">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="S11">
         <v>1.19</v>
       </c>
       <c r="T11">
-        <v>4.8</v>
+        <v>3.92</v>
       </c>
       <c r="U11">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V11">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="W11">
         <v>1.18</v>
@@ -2135,31 +2135,31 @@
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z11">
         <v>6.3</v>
       </c>
       <c r="AA11">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AB11">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="AC11">
         <v>1.97</v>
       </c>
       <c r="AD11">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AE11">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AF11">
         <v>1.42</v>
       </c>
       <c r="AG11">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK11">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2434,22 +2434,22 @@
         <v>2.7</v>
       </c>
       <c r="P13">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q13">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="R13">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="S13">
         <v>1.58</v>
       </c>
       <c r="T13">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="U13">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="V13">
         <v>1.25</v>
@@ -2461,10 +2461,10 @@
         <v>1.13</v>
       </c>
       <c r="Y13">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Z13">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AA13">
         <v>2.82</v>
@@ -2476,16 +2476,16 @@
         <v>5.53</v>
       </c>
       <c r="AD13">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE13">
         <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AG13">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK13">
         <v>1.27</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="O15">
-        <v>3.92</v>
+        <v>3.42</v>
       </c>
       <c r="P15">
-        <v>3.6</v>
+        <v>3.19</v>
       </c>
       <c r="Q15">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="R15">
         <v>2.5</v>
       </c>
       <c r="S15">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T15">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="U15">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="V15">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W15">
         <v>1.12</v>
@@ -2787,25 +2787,25 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z15">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="AA15">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AB15">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="AC15">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AD15">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE15">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF15">
         <v>1.44</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK15">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="O16">
-        <v>4.72</v>
+        <v>4.6</v>
       </c>
       <c r="P16">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Q16">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R16">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="S16">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T16">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="U16">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="V16">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W16">
         <v>1.12</v>
@@ -2950,31 +2950,31 @@
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z16">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AA16">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AB16">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AC16">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AD16">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE16">
         <v>1.2</v>
       </c>
       <c r="AF16">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AG16">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK16">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="O17">
-        <v>6.65</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>11</v>
@@ -3092,28 +3092,28 @@
         <v>1.54</v>
       </c>
       <c r="R17">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T17">
         <v>3.7</v>
       </c>
       <c r="U17">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V17">
         <v>1.58</v>
       </c>
       <c r="W17">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z17">
         <v>4.64</v>
@@ -3131,13 +3131,13 @@
         <v>1.55</v>
       </c>
       <c r="AE17">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF17">
         <v>2.15</v>
       </c>
       <c r="AG17">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK17">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="O18">
-        <v>3.55</v>
+        <v>3.71</v>
       </c>
       <c r="P18">
-        <v>3.06</v>
+        <v>2.68</v>
       </c>
       <c r="Q18">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="R18">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S18">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="U18">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V18">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="AA18">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB18">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AC18">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AD18">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE18">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF18">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AG18">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.36</v>
       </c>
       <c r="AK18">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.27</v>
+        <v>1.84</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P19">
-        <v>2.86</v>
+        <v>3.9</v>
       </c>
       <c r="Q19">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="R19">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="S19">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="T19">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W19">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA19">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB19">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC19">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="AD19">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE19">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF19">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="O20">
-        <v>3.74</v>
+        <v>3.35</v>
       </c>
       <c r="P20">
-        <v>3.84</v>
+        <v>3.05</v>
       </c>
       <c r="Q20">
-        <v>2.37</v>
+        <v>2.64</v>
       </c>
       <c r="R20">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="S20">
         <v>1.37</v>
@@ -3590,59 +3590,59 @@
         <v>2.8</v>
       </c>
       <c r="U20">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="V20">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
         <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z20">
-        <v>3.78</v>
+        <v>3.45</v>
       </c>
       <c r="AA20">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB20">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AC20">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD20">
+        <v>1.29</v>
+      </c>
+      <c r="AE20">
+        <v>1.07</v>
+      </c>
+      <c r="AF20">
+        <v>1.7</v>
+      </c>
+      <c r="AG20">
+        <v>2.1</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.3</v>
       </c>
-      <c r="AE20">
-        <v>1.09</v>
-      </c>
-      <c r="AF20">
-        <v>1.76</v>
-      </c>
-      <c r="AG20">
-        <v>1.96</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.25</v>
-      </c>
       <c r="AK20">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="O21">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
       <c r="Q21">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S21">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T21">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="U21">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z21">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AA21">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AB21">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="AC21">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD21">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AE21">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AG21">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
       <c r="O22">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="P22">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S22">
         <v>1.35</v>
       </c>
       <c r="T22">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="U22">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="V22">
         <v>1.43</v>
       </c>
       <c r="W22">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
         <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z22">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA22">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB22">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC22">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="AD22">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE22">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
         <v>1.66</v>
       </c>
       <c r="AG22">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O24">
         <v>3.9</v>
       </c>
       <c r="P24">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="Q24">
         <v>4</v>
@@ -4245,7 +4245,7 @@
         <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
         <v>1.13</v>
@@ -4263,13 +4263,13 @@
         <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AC24">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AD24">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
         <v>1.14</v>
@@ -4278,7 +4278,7 @@
         <v>1.61</v>
       </c>
       <c r="AG24">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.27</v>
+        <v>2</v>
       </c>
       <c r="AK24">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="O25">
-        <v>4.26</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="Q25">
-        <v>2.09</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
+        <v>1.3</v>
+      </c>
+      <c r="T25">
+        <v>3.12</v>
+      </c>
+      <c r="U25">
+        <v>2.6</v>
+      </c>
+      <c r="V25">
+        <v>1.48</v>
+      </c>
+      <c r="W25">
+        <v>1.09</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
         <v>1.25</v>
       </c>
-      <c r="T25">
-        <v>3.66</v>
-      </c>
-      <c r="U25">
-        <v>2.25</v>
-      </c>
-      <c r="V25">
-        <v>1.6</v>
-      </c>
-      <c r="W25">
-        <v>1.13</v>
-      </c>
-      <c r="X25">
-        <v>1.01</v>
-      </c>
-      <c r="Y25">
-        <v>1.16</v>
-      </c>
       <c r="Z25">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA25">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AB25">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="AC25">
-        <v>2.4</v>
+        <v>3.02</v>
       </c>
       <c r="AD25">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AE25">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG25">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AK25">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.19</v>
+        <v>1.62</v>
       </c>
       <c r="O26">
-        <v>3.45</v>
+        <v>4.24</v>
       </c>
       <c r="P26">
-        <v>2.93</v>
+        <v>4.6</v>
       </c>
       <c r="Q26">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="R26">
+        <v>2.5</v>
+      </c>
+      <c r="S26">
+        <v>1.25</v>
+      </c>
+      <c r="T26">
+        <v>3.35</v>
+      </c>
+      <c r="U26">
         <v>2.25</v>
       </c>
-      <c r="S26">
-        <v>1.3</v>
-      </c>
-      <c r="T26">
-        <v>3.21</v>
-      </c>
-      <c r="U26">
-        <v>2.49</v>
-      </c>
       <c r="V26">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
+        <v>1.16</v>
+      </c>
+      <c r="Z26">
+        <v>5.2</v>
+      </c>
+      <c r="AA26">
+        <v>1.55</v>
+      </c>
+      <c r="AB26">
+        <v>2.45</v>
+      </c>
+      <c r="AC26">
+        <v>2.4</v>
+      </c>
+      <c r="AD26">
+        <v>1.57</v>
+      </c>
+      <c r="AE26">
+        <v>1.22</v>
+      </c>
+      <c r="AF26">
+        <v>1.55</v>
+      </c>
+      <c r="AG26">
+        <v>2.45</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
         <v>1.25</v>
       </c>
-      <c r="Z26">
-        <v>3.9</v>
-      </c>
-      <c r="AA26">
-        <v>1.82</v>
-      </c>
-      <c r="AB26">
-        <v>2.01</v>
-      </c>
-      <c r="AC26">
-        <v>2.96</v>
-      </c>
-      <c r="AD26">
-        <v>1.35</v>
-      </c>
-      <c r="AE26">
-        <v>1.1</v>
-      </c>
-      <c r="AF26">
-        <v>1.62</v>
-      </c>
-      <c r="AG26">
-        <v>2.15</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.37</v>
-      </c>
       <c r="AK26">
-        <v>1.65</v>
+        <v>2.32</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4713,16 +4713,16 @@
         <v>1.8</v>
       </c>
       <c r="O27">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P27">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q27">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R27">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="S27">
         <v>1.2</v>
@@ -4731,43 +4731,43 @@
         <v>4</v>
       </c>
       <c r="U27">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="V27">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W27">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z27">
         <v>4.75</v>
       </c>
       <c r="AA27">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB27">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AC27">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AD27">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE27">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF27">
         <v>1.53</v>
       </c>
       <c r="AG27">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK27">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>4.29</v>
+        <v>4.82</v>
       </c>
       <c r="O28">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P28">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="Q28">
-        <v>4.75</v>
+        <v>4.92</v>
       </c>
       <c r="R28">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S28">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="U28">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="V28">
+        <v>1.57</v>
+      </c>
+      <c r="W28">
+        <v>1.12</v>
+      </c>
+      <c r="X28">
+        <v>1.03</v>
+      </c>
+      <c r="Y28">
+        <v>1.14</v>
+      </c>
+      <c r="Z28">
+        <v>4.4</v>
+      </c>
+      <c r="AA28">
         <v>1.52</v>
       </c>
-      <c r="W28">
-        <v>1.1</v>
-      </c>
-      <c r="X28">
-        <v>1.02</v>
-      </c>
-      <c r="Y28">
-        <v>1.22</v>
-      </c>
-      <c r="Z28">
-        <v>4.05</v>
-      </c>
-      <c r="AA28">
-        <v>1.63</v>
-      </c>
       <c r="AB28">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AC28">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AD28">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF28">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG28">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.23</v>
       </c>
       <c r="AK28">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="O29">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P31">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="O32">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="O33">
         <v>3.25</v>
       </c>
       <c r="P33">
-        <v>4.2</v>
+        <v>5.15</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -5718,7 +5718,7 @@
         <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y33">
         <v>1.51</v>
@@ -5727,13 +5727,13 @@
         <v>2.52</v>
       </c>
       <c r="AA33">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="AB33">
         <v>1.48</v>
       </c>
       <c r="AC33">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AD33">
         <v>1.13</v>
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5954,169 +5954,6 @@
         <v>0</v>
       </c>
       <c r="AU34" t="inlineStr">
-        <is>
-          <t>2026-09-08 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N35">
-        <v>2.05</v>
-      </c>
-      <c r="O35">
-        <v>2.9</v>
-      </c>
-      <c r="P35">
-        <v>3.5</v>
-      </c>
-      <c r="Q35">
-        <v>2.88</v>
-      </c>
-      <c r="R35">
-        <v>1.73</v>
-      </c>
-      <c r="S35">
-        <v>1.67</v>
-      </c>
-      <c r="T35">
-        <v>2.11</v>
-      </c>
-      <c r="U35">
-        <v>4.1</v>
-      </c>
-      <c r="V35">
-        <v>1.2</v>
-      </c>
-      <c r="W35">
-        <v>1.04</v>
-      </c>
-      <c r="X35">
-        <v>1.14</v>
-      </c>
-      <c r="Y35">
-        <v>1.55</v>
-      </c>
-      <c r="Z35">
-        <v>2.44</v>
-      </c>
-      <c r="AA35">
-        <v>2.52</v>
-      </c>
-      <c r="AB35">
-        <v>1.43</v>
-      </c>
-      <c r="AC35">
-        <v>5.41</v>
-      </c>
-      <c r="AD35">
-        <v>1.12</v>
-      </c>
-      <c r="AE35">
-        <v>1.04</v>
-      </c>
-      <c r="AF35">
-        <v>2.25</v>
-      </c>
-      <c r="AG35">
-        <v>1.59</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.41</v>
-      </c>
-      <c r="AK35">
-        <v>1.68</v>
-      </c>
-      <c r="AL35">
-        <v>0</v>
-      </c>
-      <c r="AM35">
-        <v>-1</v>
-      </c>
-      <c r="AN35">
-        <v>-1</v>
-      </c>
-      <c r="AO35">
-        <v>-1</v>
-      </c>
-      <c r="AP35">
-        <v>-1</v>
-      </c>
-      <c r="AQ35">
-        <v>0</v>
-      </c>
-      <c r="AR35">
-        <v>0</v>
-      </c>
-      <c r="AS35">
-        <v>0</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
         <is>
           <t>2026-09-08 21:30:00</t>
         </is>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="O7">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P7">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q7">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="R7">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
         <v>1.26</v>
@@ -1471,13 +1471,13 @@
         <v>3.32</v>
       </c>
       <c r="U7">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V7">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
         <v>1.01</v>
@@ -1492,22 +1492,22 @@
         <v>1.6</v>
       </c>
       <c r="AB7">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AC7">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="AD7">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AE7">
         <v>1.16</v>
       </c>
       <c r="AF7">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG7">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK7">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O13">
         <v>2.7</v>
       </c>
       <c r="P13">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q13">
-        <v>4.15</v>
+        <v>4.22</v>
       </c>
       <c r="R13">
         <v>1.83</v>
@@ -2449,43 +2449,43 @@
         <v>2.22</v>
       </c>
       <c r="U13">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="V13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y13">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Z13">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AA13">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AB13">
         <v>1.41</v>
       </c>
       <c r="AC13">
-        <v>5.53</v>
+        <v>5.35</v>
       </c>
       <c r="AD13">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AE13">
         <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AG13">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK13">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,34 +2754,34 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="O15">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="P15">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="Q15">
+        <v>2.46</v>
+      </c>
+      <c r="R15">
         <v>2.38</v>
       </c>
-      <c r="R15">
-        <v>2.5</v>
-      </c>
       <c r="S15">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="V15">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1.02</v>
@@ -2790,28 +2790,28 @@
         <v>1.1</v>
       </c>
       <c r="Z15">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="AA15">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AB15">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="AC15">
         <v>2.23</v>
       </c>
       <c r="AD15">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE15">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AF15">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG15">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK15">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2929,16 +2929,16 @@
         <v>1.85</v>
       </c>
       <c r="R16">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="S16">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T16">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="U16">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="V16">
         <v>1.65</v>
@@ -2947,34 +2947,34 @@
         <v>1.12</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z16">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA16">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AB16">
         <v>2.46</v>
       </c>
       <c r="AC16">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="AD16">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE16">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF16">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK16">
         <v>2.63</v>
@@ -3246,13 +3246,13 @@
         <v>2.06</v>
       </c>
       <c r="O18">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="Q18">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="R18">
         <v>2.32</v>
@@ -3264,43 +3264,43 @@
         <v>3.8</v>
       </c>
       <c r="U18">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V18">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W18">
         <v>1.11</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
         <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>4.5</v>
+        <v>5.07</v>
       </c>
       <c r="AA18">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB18">
         <v>2.3</v>
       </c>
       <c r="AC18">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AD18">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE18">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF18">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG18">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3412,13 +3412,13 @@
         <v>3.7</v>
       </c>
       <c r="P19">
-        <v>3.9</v>
+        <v>3.99</v>
       </c>
       <c r="Q19">
         <v>2.38</v>
       </c>
       <c r="R19">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="S19">
         <v>1.32</v>
@@ -3427,13 +3427,13 @@
         <v>3.1</v>
       </c>
       <c r="U19">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="V19">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
         <v>1.03</v>
@@ -3442,13 +3442,13 @@
         <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA19">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB19">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC19">
         <v>3.05</v>
@@ -3457,13 +3457,13 @@
         <v>1.42</v>
       </c>
       <c r="AE19">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="O20">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P20">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="Q20">
-        <v>2.64</v>
+        <v>2.37</v>
       </c>
       <c r="R20">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="S20">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T20">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="U20">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
         <v>1</v>
@@ -3608,19 +3608,19 @@
         <v>3.45</v>
       </c>
       <c r="AA20">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AB20">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AC20">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="AD20">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF20">
         <v>1.7</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>2.05</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>3.01</v>
+        <v>3.4</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
@@ -3747,43 +3747,43 @@
         <v>2.25</v>
       </c>
       <c r="S21">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T21">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U21">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V21">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W21">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
         <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z21">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="AA21">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB21">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AC21">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD21">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE21">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF21">
         <v>1.64</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK21">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,49 +3895,49 @@
         </is>
       </c>
       <c r="N22">
+        <v>3.1</v>
+      </c>
+      <c r="O22">
+        <v>3.4</v>
+      </c>
+      <c r="P22">
+        <v>2.23</v>
+      </c>
+      <c r="Q22">
+        <v>3.5</v>
+      </c>
+      <c r="R22">
+        <v>2.2</v>
+      </c>
+      <c r="S22">
+        <v>1.38</v>
+      </c>
+      <c r="T22">
+        <v>2.74</v>
+      </c>
+      <c r="U22">
         <v>2.73</v>
-      </c>
-      <c r="O22">
-        <v>3.47</v>
-      </c>
-      <c r="P22">
-        <v>2.13</v>
-      </c>
-      <c r="Q22">
-        <v>3.3</v>
-      </c>
-      <c r="R22">
-        <v>2.15</v>
-      </c>
-      <c r="S22">
-        <v>1.35</v>
-      </c>
-      <c r="T22">
-        <v>3.13</v>
-      </c>
-      <c r="U22">
-        <v>2.76</v>
       </c>
       <c r="V22">
         <v>1.43</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
         <v>1.29</v>
       </c>
       <c r="Z22">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="AA22">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AB22">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC22">
         <v>3.15</v>
@@ -3946,10 +3946,10 @@
         <v>1.36</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG22">
         <v>2.1</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AK22">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>4.82</v>
+        <v>4.45</v>
       </c>
       <c r="O28">
         <v>4.2</v>
@@ -4882,19 +4882,19 @@
         <v>1.64</v>
       </c>
       <c r="Q28">
-        <v>4.92</v>
+        <v>4.88</v>
       </c>
       <c r="R28">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T28">
         <v>3.34</v>
       </c>
       <c r="U28">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="V28">
         <v>1.57</v>
@@ -4903,13 +4903,13 @@
         <v>1.12</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
         <v>1.14</v>
       </c>
       <c r="Z28">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA28">
         <v>1.52</v>
@@ -4918,16 +4918,16 @@
         <v>2.25</v>
       </c>
       <c r="AC28">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD28">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE28">
         <v>1.18</v>
       </c>
       <c r="AF28">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG28">
         <v>2.25</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.23</v>
+        <v>2.24</v>
       </c>
       <c r="AK28">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O29">
+        <v>3</v>
+      </c>
+      <c r="P29">
         <v>3.1</v>
-      </c>
-      <c r="P29">
-        <v>3.15</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5208,10 +5208,10 @@
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -5220,10 +5220,10 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W30">
         <v>0</v>
@@ -5232,31 +5232,31 @@
         <v>0</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O31">
         <v>3.25</v>
       </c>
       <c r="P31">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="O32">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P32">
+        <v>2.6</v>
+      </c>
+      <c r="Q32">
+        <v>2.99</v>
+      </c>
+      <c r="R32">
+        <v>2.1</v>
+      </c>
+      <c r="S32">
+        <v>1.33</v>
+      </c>
+      <c r="T32">
+        <v>2.9</v>
+      </c>
+      <c r="U32">
         <v>2.7</v>
       </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL32">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="P2">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="Q2">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T2">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="U2">
         <v>3.04</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
         <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AA2">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB2">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AC2">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="AD2">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG2">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,55 +807,55 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>3.85</v>
+        <v>3.28</v>
       </c>
       <c r="R3">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
-        <v>3.04</v>
+        <v>3.23</v>
       </c>
       <c r="U3">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="AA3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB3">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AC3">
         <v>2.63</v>
       </c>
       <c r="AD3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG3">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.55</v>
+        <v>4.75</v>
       </c>
       <c r="O5">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="Q5">
-        <v>4.24</v>
+        <v>4.8</v>
       </c>
       <c r="R5">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="U5">
         <v>2.1</v>
       </c>
       <c r="V5">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W5">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AB5">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AC5">
         <v>2.2</v>
       </c>
       <c r="AD5">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AE5">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AF5">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="O6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P6">
-        <v>4.9</v>
+        <v>4.93</v>
       </c>
       <c r="Q6">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="R6">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="S6">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T6">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="U6">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="V6">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W6">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z6">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB6">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="AC6">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD6">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AE6">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF6">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AG6">
+        <v>2.29</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.08</v>
+      </c>
+      <c r="AK6">
         <v>2.5</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.14</v>
-      </c>
-      <c r="AK6">
-        <v>2.24</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="Q7">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="U7">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="V7">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA7">
         <v>1.6</v>
       </c>
       <c r="AB7">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AC7">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AD7">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE7">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF7">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG7">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.72</v>
+        <v>1.8</v>
       </c>
       <c r="O9">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="P9">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q9">
-        <v>3.01</v>
+        <v>2.34</v>
       </c>
       <c r="R9">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="S9">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T9">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="U9">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
         <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AA9">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB9">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AC9">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AD9">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AE9">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG9">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="AK9">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,65 +1939,65 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="O10">
+        <v>3.5</v>
+      </c>
+      <c r="P10">
+        <v>2.27</v>
+      </c>
+      <c r="Q10">
+        <v>3.45</v>
+      </c>
+      <c r="R10">
+        <v>2.3</v>
+      </c>
+      <c r="S10">
+        <v>1.33</v>
+      </c>
+      <c r="T10">
+        <v>3.3</v>
+      </c>
+      <c r="U10">
+        <v>2.49</v>
+      </c>
+      <c r="V10">
+        <v>1.5</v>
+      </c>
+      <c r="W10">
+        <v>1.08</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1.2</v>
+      </c>
+      <c r="Z10">
         <v>3.98</v>
       </c>
-      <c r="P10">
-        <v>3.75</v>
-      </c>
-      <c r="Q10">
-        <v>2.33</v>
-      </c>
-      <c r="R10">
-        <v>2.52</v>
-      </c>
-      <c r="S10">
-        <v>1.31</v>
-      </c>
-      <c r="T10">
-        <v>3.05</v>
-      </c>
-      <c r="U10">
-        <v>2.4</v>
-      </c>
-      <c r="V10">
-        <v>1.54</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.02</v>
-      </c>
-      <c r="Y10">
-        <v>1.16</v>
-      </c>
-      <c r="Z10">
-        <v>4.5</v>
-      </c>
       <c r="AA10">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AB10">
+        <v>2.19</v>
+      </c>
+      <c r="AC10">
+        <v>2.64</v>
+      </c>
+      <c r="AD10">
+        <v>1.41</v>
+      </c>
+      <c r="AE10">
+        <v>1.12</v>
+      </c>
+      <c r="AF10">
+        <v>1.57</v>
+      </c>
+      <c r="AG10">
         <v>2.3</v>
       </c>
-      <c r="AC10">
-        <v>2.51</v>
-      </c>
-      <c r="AD10">
-        <v>1.48</v>
-      </c>
-      <c r="AE10">
-        <v>1.13</v>
-      </c>
-      <c r="AF10">
-        <v>1.64</v>
-      </c>
-      <c r="AG10">
-        <v>2.2</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AK10">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2271,55 +2271,55 @@
         <v>3.8</v>
       </c>
       <c r="P12">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S12">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="U12">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="V12">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z12">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA12">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AB12">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC12">
-        <v>3.92</v>
+        <v>3.77</v>
       </c>
       <c r="AD12">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE12">
         <v>1.02</v>
       </c>
       <c r="AF12">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AG12">
         <v>1.53</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O13">
         <v>2.7</v>
@@ -2437,55 +2437,55 @@
         <v>2.3</v>
       </c>
       <c r="Q13">
-        <v>4.22</v>
+        <v>4.38</v>
       </c>
       <c r="R13">
         <v>1.83</v>
       </c>
       <c r="S13">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T13">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U13">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="V13">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W13">
         <v>1.02</v>
       </c>
       <c r="X13">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y13">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z13">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AA13">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="AB13">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AC13">
-        <v>5.35</v>
+        <v>6</v>
       </c>
       <c r="AD13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE13">
         <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AG13">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
+        <v>1.98</v>
+      </c>
+      <c r="O14">
+        <v>3.75</v>
+      </c>
+      <c r="P14">
+        <v>3.25</v>
+      </c>
+      <c r="Q14">
         <v>2.45</v>
       </c>
-      <c r="O14">
-        <v>2.8</v>
-      </c>
-      <c r="P14">
-        <v>2.74</v>
-      </c>
-      <c r="Q14">
-        <v>3.28</v>
-      </c>
       <c r="R14">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="T14">
-        <v>2.31</v>
+        <v>3.42</v>
       </c>
       <c r="U14">
-        <v>3.42</v>
+        <v>2.15</v>
       </c>
       <c r="V14">
+        <v>1.62</v>
+      </c>
+      <c r="W14">
+        <v>1.11</v>
+      </c>
+      <c r="X14">
+        <v>1.02</v>
+      </c>
+      <c r="Y14">
+        <v>1.17</v>
+      </c>
+      <c r="Z14">
+        <v>5</v>
+      </c>
+      <c r="AA14">
+        <v>1.43</v>
+      </c>
+      <c r="AB14">
+        <v>2.38</v>
+      </c>
+      <c r="AC14">
+        <v>2.1</v>
+      </c>
+      <c r="AD14">
+        <v>1.59</v>
+      </c>
+      <c r="AE14">
         <v>1.24</v>
       </c>
-      <c r="W14">
-        <v>1.01</v>
-      </c>
-      <c r="X14">
-        <v>1.04</v>
-      </c>
-      <c r="Y14">
+      <c r="AF14">
         <v>1.43</v>
       </c>
-      <c r="Z14">
-        <v>2.58</v>
-      </c>
-      <c r="AA14">
-        <v>2.33</v>
-      </c>
-      <c r="AB14">
-        <v>1.48</v>
-      </c>
-      <c r="AC14">
-        <v>4.5</v>
-      </c>
-      <c r="AD14">
-        <v>1.13</v>
-      </c>
-      <c r="AE14">
-        <v>1.03</v>
-      </c>
-      <c r="AF14">
-        <v>1.96</v>
-      </c>
       <c r="AG14">
-        <v>1.73</v>
+        <v>2.55</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00:00</t>
+          <t>2026-09-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.91</v>
+        <v>1.43</v>
       </c>
       <c r="O15">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="P15">
-        <v>3.6</v>
+        <v>5.65</v>
       </c>
       <c r="Q15">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="R15">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="S15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T15">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U15">
         <v>2.1</v>
       </c>
       <c r="V15">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA15">
         <v>1.46</v>
       </c>
       <c r="AB15">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AC15">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AD15">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE15">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AF15">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AG15">
-        <v>2.59</v>
+        <v>2.19</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK15">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.43</v>
+        <v>2.45</v>
       </c>
       <c r="O16">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="P16">
-        <v>5.75</v>
+        <v>2.74</v>
       </c>
       <c r="Q16">
-        <v>1.85</v>
+        <v>3.36</v>
       </c>
       <c r="R16">
-        <v>2.51</v>
+        <v>1.79</v>
       </c>
       <c r="S16">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="T16">
-        <v>3.7</v>
+        <v>2.24</v>
       </c>
       <c r="U16">
-        <v>2.13</v>
+        <v>3.6</v>
       </c>
       <c r="V16">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y16">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="Z16">
-        <v>5.25</v>
+        <v>2.44</v>
       </c>
       <c r="AA16">
-        <v>1.45</v>
+        <v>2.46</v>
       </c>
       <c r="AB16">
-        <v>2.46</v>
+        <v>1.57</v>
       </c>
       <c r="AC16">
-        <v>2.12</v>
+        <v>4.9</v>
       </c>
       <c r="AD16">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="AE16">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="AG16">
-        <v>2.38</v>
+        <v>1.66</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AK16">
-        <v>2.63</v>
+        <v>1.4</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3086,58 +3086,58 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="Q17">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R17">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="S17">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U17">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V17">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="W17">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z17">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
       <c r="AA17">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AB17">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AC17">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AD17">
         <v>1.55</v>
       </c>
       <c r="AE17">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF17">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG17">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK17">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,58 +3406,58 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="O19">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P19">
-        <v>3.99</v>
+        <v>3.08</v>
       </c>
       <c r="Q19">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="R19">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="S19">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U19">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="V19">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z19">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="AA19">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AB19">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="AC19">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="AD19">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF19">
         <v>1.7</v>
@@ -3479,7 +3479,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O20">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="Q20">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="R20">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="U20">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W20">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z20">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="AA20">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB20">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="AC20">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="AD20">
         <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
+        <v>1.64</v>
+      </c>
+      <c r="AG20">
+        <v>2.23</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.27</v>
+      </c>
+      <c r="AK20">
         <v>1.7</v>
-      </c>
-      <c r="AG20">
-        <v>2.1</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.25</v>
-      </c>
-      <c r="AK20">
-        <v>1.75</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="O21">
+        <v>3.4</v>
+      </c>
+      <c r="P21">
+        <v>2.23</v>
+      </c>
+      <c r="Q21">
         <v>3.5</v>
       </c>
-      <c r="P21">
-        <v>3.4</v>
-      </c>
-      <c r="Q21">
-        <v>2.5</v>
-      </c>
       <c r="R21">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S21">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T21">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="U21">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="V21">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
         <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z21">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AA21">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AB21">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AC21">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="AD21">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE21">
         <v>1.1</v>
       </c>
       <c r="AF21">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG21">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="AK21">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,61 +3895,61 @@
         </is>
       </c>
       <c r="N22">
+        <v>1.84</v>
+      </c>
+      <c r="O22">
+        <v>3.7</v>
+      </c>
+      <c r="P22">
+        <v>3.99</v>
+      </c>
+      <c r="Q22">
+        <v>2.38</v>
+      </c>
+      <c r="R22">
+        <v>2.23</v>
+      </c>
+      <c r="S22">
+        <v>1.32</v>
+      </c>
+      <c r="T22">
         <v>3.1</v>
       </c>
-      <c r="O22">
-        <v>3.4</v>
-      </c>
-      <c r="P22">
-        <v>2.23</v>
-      </c>
-      <c r="Q22">
-        <v>3.5</v>
-      </c>
-      <c r="R22">
-        <v>2.2</v>
-      </c>
-      <c r="S22">
-        <v>1.38</v>
-      </c>
-      <c r="T22">
-        <v>2.74</v>
-      </c>
       <c r="U22">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="V22">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W22">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z22">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AA22">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AB22">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AC22">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AD22">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE22">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG22">
         <v>2.1</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>4.6</v>
+        <v>2.19</v>
       </c>
       <c r="O24">
+        <v>3.46</v>
+      </c>
+      <c r="P24">
+        <v>3.25</v>
+      </c>
+      <c r="Q24">
+        <v>2.59</v>
+      </c>
+      <c r="R24">
+        <v>2.21</v>
+      </c>
+      <c r="S24">
+        <v>1.36</v>
+      </c>
+      <c r="T24">
+        <v>2.82</v>
+      </c>
+      <c r="U24">
+        <v>2.68</v>
+      </c>
+      <c r="V24">
+        <v>1.46</v>
+      </c>
+      <c r="W24">
+        <v>1.07</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1.26</v>
+      </c>
+      <c r="Z24">
         <v>3.9</v>
       </c>
-      <c r="P24">
-        <v>1.67</v>
-      </c>
-      <c r="Q24">
-        <v>4</v>
-      </c>
-      <c r="R24">
-        <v>2.3</v>
-      </c>
-      <c r="S24">
-        <v>1.28</v>
-      </c>
-      <c r="T24">
-        <v>3.3</v>
-      </c>
-      <c r="U24">
-        <v>2.3</v>
-      </c>
-      <c r="V24">
-        <v>1.55</v>
-      </c>
-      <c r="W24">
-        <v>1.13</v>
-      </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
-      <c r="Y24">
-        <v>1.2</v>
-      </c>
-      <c r="Z24">
-        <v>4.4</v>
-      </c>
       <c r="AA24">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AB24">
-        <v>2.24</v>
+        <v>2.01</v>
       </c>
       <c r="AC24">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AE24">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AG24">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.14</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.25</v>
+        <v>1.59</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>4.44</v>
       </c>
       <c r="P25">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="Q25">
+        <v>2</v>
+      </c>
+      <c r="R25">
+        <v>2.53</v>
+      </c>
+      <c r="S25">
+        <v>1.24</v>
+      </c>
+      <c r="T25">
+        <v>4.05</v>
+      </c>
+      <c r="U25">
+        <v>2.1</v>
+      </c>
+      <c r="V25">
+        <v>1.77</v>
+      </c>
+      <c r="W25">
+        <v>1.19</v>
+      </c>
+      <c r="X25">
+        <v>1.01</v>
+      </c>
+      <c r="Y25">
+        <v>1.11</v>
+      </c>
+      <c r="Z25">
+        <v>6.5</v>
+      </c>
+      <c r="AA25">
+        <v>1.41</v>
+      </c>
+      <c r="AB25">
         <v>2.75</v>
       </c>
-      <c r="R25">
-        <v>2.25</v>
-      </c>
-      <c r="S25">
-        <v>1.3</v>
-      </c>
-      <c r="T25">
-        <v>3.12</v>
-      </c>
-      <c r="U25">
-        <v>2.6</v>
-      </c>
-      <c r="V25">
-        <v>1.48</v>
-      </c>
-      <c r="W25">
-        <v>1.09</v>
-      </c>
-      <c r="X25">
-        <v>1</v>
-      </c>
-      <c r="Y25">
-        <v>1.25</v>
-      </c>
-      <c r="Z25">
-        <v>3.9</v>
-      </c>
-      <c r="AA25">
-        <v>1.82</v>
-      </c>
-      <c r="AB25">
-        <v>2.01</v>
-      </c>
       <c r="AC25">
-        <v>3.02</v>
+        <v>2.05</v>
       </c>
       <c r="AD25">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="AE25">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="AF25">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG25">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="O26">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="P26">
-        <v>4.6</v>
+        <v>3.88</v>
       </c>
       <c r="Q26">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="R26">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S26">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T26">
         <v>3.35</v>
       </c>
       <c r="U26">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="V26">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="W26">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z26">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="AA26">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB26">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="AC26">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="AD26">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AE26">
         <v>1.22</v>
       </c>
       <c r="AF26">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG26">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="O27">
         <v>4</v>
       </c>
       <c r="P27">
-        <v>4.2</v>
+        <v>1.73</v>
       </c>
       <c r="Q27">
+        <v>4</v>
+      </c>
+      <c r="R27">
+        <v>2.3</v>
+      </c>
+      <c r="S27">
+        <v>1.29</v>
+      </c>
+      <c r="T27">
+        <v>3.42</v>
+      </c>
+      <c r="U27">
+        <v>2.4</v>
+      </c>
+      <c r="V27">
+        <v>1.52</v>
+      </c>
+      <c r="W27">
+        <v>1.1</v>
+      </c>
+      <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>1.18</v>
+      </c>
+      <c r="Z27">
+        <v>4.5</v>
+      </c>
+      <c r="AA27">
+        <v>1.6</v>
+      </c>
+      <c r="AB27">
         <v>2.24</v>
       </c>
-      <c r="R27">
-        <v>2.62</v>
-      </c>
-      <c r="S27">
-        <v>1.2</v>
-      </c>
-      <c r="T27">
-        <v>4</v>
-      </c>
-      <c r="U27">
-        <v>2.19</v>
-      </c>
-      <c r="V27">
-        <v>1.64</v>
-      </c>
-      <c r="W27">
-        <v>1.17</v>
-      </c>
-      <c r="X27">
-        <v>1.02</v>
-      </c>
-      <c r="Y27">
-        <v>1.1</v>
-      </c>
-      <c r="Z27">
-        <v>4.75</v>
-      </c>
-      <c r="AA27">
-        <v>1.46</v>
-      </c>
-      <c r="AB27">
-        <v>2.45</v>
-      </c>
       <c r="AC27">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="AD27">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AE27">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="AK27">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,49 +5036,49 @@
         </is>
       </c>
       <c r="N29">
+        <v>2.24</v>
+      </c>
+      <c r="O29">
+        <v>3.05</v>
+      </c>
+      <c r="P29">
+        <v>3.05</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
         <v>2.15</v>
       </c>
-      <c r="O29">
-        <v>3</v>
-      </c>
-      <c r="P29">
-        <v>3.1</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>0</v>
-      </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O31">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="Q31">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R31">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T31">
+        <v>2.7</v>
+      </c>
+      <c r="U31">
+        <v>2.91</v>
+      </c>
+      <c r="V31">
+        <v>1.33</v>
+      </c>
+      <c r="W31">
+        <v>1.04</v>
+      </c>
+      <c r="X31">
+        <v>1.02</v>
+      </c>
+      <c r="Y31">
+        <v>1.25</v>
+      </c>
+      <c r="Z31">
         <v>3.08</v>
       </c>
-      <c r="U31">
-        <v>2.5</v>
-      </c>
-      <c r="V31">
-        <v>1.5</v>
-      </c>
-      <c r="W31">
-        <v>1.1</v>
-      </c>
-      <c r="X31">
-        <v>1.03</v>
-      </c>
-      <c r="Y31">
-        <v>1.18</v>
-      </c>
-      <c r="Z31">
-        <v>3.84</v>
-      </c>
       <c r="AA31">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AB31">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC31">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AD31">
+        <v>1.22</v>
+      </c>
+      <c r="AE31">
+        <v>1.04</v>
+      </c>
+      <c r="AF31">
+        <v>1.83</v>
+      </c>
+      <c r="AG31">
+        <v>1.92</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.34</v>
       </c>
-      <c r="AE31">
-        <v>1.09</v>
-      </c>
-      <c r="AF31">
-        <v>1.58</v>
-      </c>
-      <c r="AG31">
-        <v>2.21</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.23</v>
-      </c>
       <c r="AK31">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="O32">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P32">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="Q32">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="V32">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
         <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA32">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB32">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC32">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="AD32">
         <v>1.28</v>
       </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF32">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,25 +5691,25 @@
         <v>1.8</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P33">
-        <v>5.15</v>
+        <v>3.78</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
       </c>
       <c r="R33">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="S33">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T33">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="U33">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="V33">
         <v>1.22</v>
@@ -5718,34 +5718,34 @@
         <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y33">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Z33">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="AA33">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AB33">
         <v>1.48</v>
       </c>
       <c r="AC33">
-        <v>4.8</v>
+        <v>5.33</v>
       </c>
       <c r="AD33">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE33">
         <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG33">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.36</v>
       </c>
       <c r="AK33">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,22 +5851,22 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="O34">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="P34">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q34">
         <v>2.56</v>
       </c>
       <c r="R34">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S34">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="T34">
         <v>2.17</v>
@@ -5881,31 +5881,31 @@
         <v>1.02</v>
       </c>
       <c r="X34">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Y34">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z34">
         <v>2.42</v>
       </c>
       <c r="AA34">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="AB34">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AC34">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="AD34">
         <v>1.15</v>
       </c>
       <c r="AE34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AG34">
         <v>1.61</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AK34">
         <v>1.68</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,61 +3732,61 @@
         </is>
       </c>
       <c r="N21">
+        <v>1.84</v>
+      </c>
+      <c r="O21">
+        <v>3.7</v>
+      </c>
+      <c r="P21">
+        <v>3.99</v>
+      </c>
+      <c r="Q21">
+        <v>2.38</v>
+      </c>
+      <c r="R21">
+        <v>2.23</v>
+      </c>
+      <c r="S21">
+        <v>1.32</v>
+      </c>
+      <c r="T21">
         <v>3.1</v>
       </c>
-      <c r="O21">
-        <v>3.4</v>
-      </c>
-      <c r="P21">
-        <v>2.23</v>
-      </c>
-      <c r="Q21">
-        <v>3.5</v>
-      </c>
-      <c r="R21">
-        <v>2.2</v>
-      </c>
-      <c r="S21">
-        <v>1.38</v>
-      </c>
-      <c r="T21">
-        <v>2.74</v>
-      </c>
       <c r="U21">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="V21">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
         <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z21">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AA21">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AB21">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AC21">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AD21">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE21">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG21">
         <v>2.1</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,61 +3895,61 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.84</v>
+        <v>3.1</v>
       </c>
       <c r="O22">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>3.99</v>
+        <v>2.23</v>
       </c>
       <c r="Q22">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="R22">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T22">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="U22">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="V22">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z22">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AA22">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AB22">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC22">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AD22">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE22">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG22">
         <v>2.1</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AK22">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,61 +4221,61 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.19</v>
+        <v>4.3</v>
       </c>
       <c r="O24">
-        <v>3.46</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>3.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q24">
+        <v>4</v>
+      </c>
+      <c r="R24">
+        <v>2.3</v>
+      </c>
+      <c r="S24">
+        <v>1.29</v>
+      </c>
+      <c r="T24">
+        <v>3.42</v>
+      </c>
+      <c r="U24">
+        <v>2.4</v>
+      </c>
+      <c r="V24">
+        <v>1.52</v>
+      </c>
+      <c r="W24">
+        <v>1.1</v>
+      </c>
+      <c r="X24">
+        <v>1.01</v>
+      </c>
+      <c r="Y24">
+        <v>1.18</v>
+      </c>
+      <c r="Z24">
+        <v>4.5</v>
+      </c>
+      <c r="AA24">
+        <v>1.6</v>
+      </c>
+      <c r="AB24">
+        <v>2.24</v>
+      </c>
+      <c r="AC24">
         <v>2.59</v>
       </c>
-      <c r="R24">
-        <v>2.21</v>
-      </c>
-      <c r="S24">
-        <v>1.36</v>
-      </c>
-      <c r="T24">
-        <v>2.82</v>
-      </c>
-      <c r="U24">
-        <v>2.68</v>
-      </c>
-      <c r="V24">
-        <v>1.46</v>
-      </c>
-      <c r="W24">
-        <v>1.07</v>
-      </c>
-      <c r="X24">
-        <v>1</v>
-      </c>
-      <c r="Y24">
-        <v>1.26</v>
-      </c>
-      <c r="Z24">
-        <v>3.9</v>
-      </c>
-      <c r="AA24">
-        <v>1.82</v>
-      </c>
-      <c r="AB24">
-        <v>2.01</v>
-      </c>
-      <c r="AC24">
-        <v>3</v>
-      </c>
       <c r="AD24">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
         <v>2.15</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK24">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.75</v>
+        <v>2.19</v>
       </c>
       <c r="O26">
-        <v>4.2</v>
+        <v>3.46</v>
       </c>
       <c r="P26">
-        <v>3.88</v>
+        <v>3.25</v>
       </c>
       <c r="Q26">
-        <v>2.24</v>
+        <v>2.59</v>
       </c>
       <c r="R26">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="S26">
+        <v>1.36</v>
+      </c>
+      <c r="T26">
+        <v>2.82</v>
+      </c>
+      <c r="U26">
+        <v>2.68</v>
+      </c>
+      <c r="V26">
+        <v>1.46</v>
+      </c>
+      <c r="W26">
+        <v>1.07</v>
+      </c>
+      <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26">
         <v>1.26</v>
       </c>
-      <c r="T26">
-        <v>3.35</v>
-      </c>
-      <c r="U26">
-        <v>2.18</v>
-      </c>
-      <c r="V26">
-        <v>1.71</v>
-      </c>
-      <c r="W26">
-        <v>1.17</v>
-      </c>
-      <c r="X26">
-        <v>1.02</v>
-      </c>
-      <c r="Y26">
-        <v>1.11</v>
-      </c>
       <c r="Z26">
-        <v>5.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA26">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AB26">
-        <v>2.62</v>
+        <v>2.01</v>
       </c>
       <c r="AC26">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="AD26">
+        <v>1.35</v>
+      </c>
+      <c r="AE26">
+        <v>1.1</v>
+      </c>
+      <c r="AF26">
+        <v>1.64</v>
+      </c>
+      <c r="AG26">
+        <v>2.15</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.3</v>
+      </c>
+      <c r="AK26">
         <v>1.7</v>
-      </c>
-      <c r="AE26">
-        <v>1.22</v>
-      </c>
-      <c r="AF26">
-        <v>1.5</v>
-      </c>
-      <c r="AG26">
-        <v>2.56</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.25</v>
-      </c>
-      <c r="AK26">
-        <v>2</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>4.3</v>
+        <v>1.75</v>
       </c>
       <c r="O27">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P27">
-        <v>1.73</v>
+        <v>3.88</v>
       </c>
       <c r="Q27">
-        <v>4</v>
+        <v>2.24</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T27">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="U27">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="V27">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA27">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB27">
+        <v>2.62</v>
+      </c>
+      <c r="AC27">
         <v>2.24</v>
       </c>
-      <c r="AC27">
-        <v>2.59</v>
-      </c>
       <c r="AD27">
+        <v>1.7</v>
+      </c>
+      <c r="AE27">
+        <v>1.22</v>
+      </c>
+      <c r="AF27">
         <v>1.5</v>
       </c>
-      <c r="AE27">
-        <v>1.15</v>
-      </c>
-      <c r="AF27">
-        <v>1.62</v>
-      </c>
       <c r="AG27">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="O9">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>4.4</v>
+        <v>2.27</v>
       </c>
       <c r="Q9">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="R9">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="U9">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="V9">
+        <v>1.5</v>
+      </c>
+      <c r="W9">
+        <v>1.08</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1.2</v>
+      </c>
+      <c r="Z9">
+        <v>3.98</v>
+      </c>
+      <c r="AA9">
+        <v>1.76</v>
+      </c>
+      <c r="AB9">
+        <v>2.19</v>
+      </c>
+      <c r="AC9">
+        <v>2.64</v>
+      </c>
+      <c r="AD9">
+        <v>1.41</v>
+      </c>
+      <c r="AE9">
+        <v>1.12</v>
+      </c>
+      <c r="AF9">
         <v>1.57</v>
       </c>
-      <c r="W9">
-        <v>1.11</v>
-      </c>
-      <c r="X9">
-        <v>1.02</v>
-      </c>
-      <c r="Y9">
-        <v>1.18</v>
-      </c>
-      <c r="Z9">
-        <v>4.5</v>
-      </c>
-      <c r="AA9">
-        <v>1.61</v>
-      </c>
-      <c r="AB9">
-        <v>2.34</v>
-      </c>
-      <c r="AC9">
-        <v>2.49</v>
-      </c>
-      <c r="AD9">
-        <v>1.53</v>
-      </c>
-      <c r="AE9">
-        <v>1.14</v>
-      </c>
-      <c r="AF9">
-        <v>1.6</v>
-      </c>
       <c r="AG9">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AK9">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="P10">
-        <v>2.27</v>
+        <v>4.4</v>
       </c>
       <c r="Q10">
-        <v>3.45</v>
+        <v>2.34</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T10">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U10">
+        <v>2.39</v>
+      </c>
+      <c r="V10">
+        <v>1.57</v>
+      </c>
+      <c r="W10">
+        <v>1.11</v>
+      </c>
+      <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>1.18</v>
+      </c>
+      <c r="Z10">
+        <v>4.5</v>
+      </c>
+      <c r="AA10">
+        <v>1.61</v>
+      </c>
+      <c r="AB10">
+        <v>2.34</v>
+      </c>
+      <c r="AC10">
         <v>2.49</v>
       </c>
-      <c r="V10">
-        <v>1.5</v>
-      </c>
-      <c r="W10">
-        <v>1.08</v>
-      </c>
-      <c r="X10">
-        <v>1</v>
-      </c>
-      <c r="Y10">
-        <v>1.2</v>
-      </c>
-      <c r="Z10">
-        <v>3.98</v>
-      </c>
-      <c r="AA10">
-        <v>1.76</v>
-      </c>
-      <c r="AB10">
-        <v>2.19</v>
-      </c>
-      <c r="AC10">
-        <v>2.64</v>
-      </c>
       <c r="AD10">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AE10">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG10">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="AK10">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.98</v>
+        <v>1.43</v>
       </c>
       <c r="O14">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="P14">
-        <v>3.25</v>
+        <v>5.65</v>
       </c>
       <c r="Q14">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="R14">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S14">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T14">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="U14">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V14">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X14">
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA14">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AB14">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AC14">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD14">
+        <v>1.65</v>
+      </c>
+      <c r="AE14">
+        <v>1.25</v>
+      </c>
+      <c r="AF14">
         <v>1.59</v>
       </c>
-      <c r="AE14">
-        <v>1.24</v>
-      </c>
-      <c r="AF14">
-        <v>1.43</v>
-      </c>
       <c r="AG14">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK14">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.43</v>
+        <v>1.98</v>
       </c>
       <c r="O15">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="P15">
-        <v>5.65</v>
+        <v>3.25</v>
       </c>
       <c r="Q15">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="R15">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T15">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="U15">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V15">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W15">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA15">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AB15">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AC15">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD15">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AE15">
+        <v>1.24</v>
+      </c>
+      <c r="AF15">
+        <v>1.43</v>
+      </c>
+      <c r="AG15">
+        <v>2.55</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.25</v>
       </c>
-      <c r="AF15">
-        <v>1.59</v>
-      </c>
-      <c r="AG15">
-        <v>2.19</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.16</v>
-      </c>
       <c r="AK15">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,61 +3732,61 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.84</v>
+        <v>3.1</v>
       </c>
       <c r="O21">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>3.99</v>
+        <v>2.23</v>
       </c>
       <c r="Q21">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="R21">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S21">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T21">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="U21">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="V21">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
         <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z21">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AA21">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AB21">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC21">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AD21">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE21">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF21">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG21">
         <v>2.1</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AK21">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,61 +3895,61 @@
         </is>
       </c>
       <c r="N22">
+        <v>1.84</v>
+      </c>
+      <c r="O22">
+        <v>3.7</v>
+      </c>
+      <c r="P22">
+        <v>3.99</v>
+      </c>
+      <c r="Q22">
+        <v>2.38</v>
+      </c>
+      <c r="R22">
+        <v>2.23</v>
+      </c>
+      <c r="S22">
+        <v>1.32</v>
+      </c>
+      <c r="T22">
         <v>3.1</v>
       </c>
-      <c r="O22">
-        <v>3.4</v>
-      </c>
-      <c r="P22">
-        <v>2.23</v>
-      </c>
-      <c r="Q22">
-        <v>3.5</v>
-      </c>
-      <c r="R22">
-        <v>2.2</v>
-      </c>
-      <c r="S22">
-        <v>1.38</v>
-      </c>
-      <c r="T22">
-        <v>2.74</v>
-      </c>
       <c r="U22">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="V22">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W22">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z22">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AA22">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AB22">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AC22">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AD22">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE22">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG22">
         <v>2.1</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>4.3</v>
+        <v>1.75</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P24">
-        <v>1.73</v>
+        <v>3.88</v>
       </c>
       <c r="Q24">
-        <v>4</v>
+        <v>2.24</v>
       </c>
       <c r="R24">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T24">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="U24">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="V24">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA24">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB24">
+        <v>2.62</v>
+      </c>
+      <c r="AC24">
         <v>2.24</v>
       </c>
-      <c r="AC24">
-        <v>2.59</v>
-      </c>
       <c r="AD24">
+        <v>1.7</v>
+      </c>
+      <c r="AE24">
+        <v>1.22</v>
+      </c>
+      <c r="AF24">
         <v>1.5</v>
       </c>
-      <c r="AE24">
-        <v>1.15</v>
-      </c>
-      <c r="AF24">
-        <v>1.62</v>
-      </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.59</v>
+        <v>4.3</v>
       </c>
       <c r="O25">
-        <v>4.44</v>
+        <v>4</v>
       </c>
       <c r="P25">
-        <v>4.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R25">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="S25">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
-        <v>4.05</v>
+        <v>3.42</v>
       </c>
       <c r="U25">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V25">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="W25">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z25">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA25">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB25">
-        <v>2.75</v>
+        <v>2.24</v>
       </c>
       <c r="AC25">
-        <v>2.05</v>
+        <v>2.59</v>
       </c>
       <c r="AD25">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="AE25">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.23</v>
+        <v>2.1</v>
       </c>
       <c r="AK25">
-        <v>2.4</v>
+        <v>1.14</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="O27">
-        <v>4.2</v>
+        <v>4.44</v>
       </c>
       <c r="P27">
-        <v>3.88</v>
+        <v>4.7</v>
       </c>
       <c r="Q27">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="R27">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="S27">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="T27">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="U27">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V27">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="W27">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
         <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA27">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AB27">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC27">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="AD27">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AE27">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AF27">
         <v>1.5</v>
       </c>
       <c r="AG27">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK27">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="O4">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="P4">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1003,7 +1003,7 @@
         <v>1.5</v>
       </c>
       <c r="AB4">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC4">
         <v>2.53</v>
@@ -1450,28 +1450,28 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O7">
         <v>3.75</v>
       </c>
       <c r="P7">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="Q7">
         <v>2.35</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S7">
         <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="U7">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="V7">
         <v>1.5</v>
@@ -1486,7 +1486,7 @@
         <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA7">
         <v>1.6</v>
@@ -1495,19 +1495,19 @@
         <v>2.28</v>
       </c>
       <c r="AC7">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AD7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE7">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF7">
         <v>1.5</v>
       </c>
       <c r="AG7">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.16</v>
       </c>
       <c r="AK7">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB8">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P9">
-        <v>2.27</v>
+        <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="R9">
+        <v>2.51</v>
+      </c>
+      <c r="S9">
+        <v>1.3</v>
+      </c>
+      <c r="T9">
+        <v>3.4</v>
+      </c>
+      <c r="U9">
         <v>2.3</v>
       </c>
-      <c r="S9">
-        <v>1.33</v>
-      </c>
-      <c r="T9">
-        <v>3.3</v>
-      </c>
-      <c r="U9">
-        <v>2.49</v>
-      </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
         <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>3.98</v>
+        <v>4.5</v>
       </c>
       <c r="AA9">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AB9">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AC9">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
       <c r="AD9">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF9">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG9">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="AK9">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="O10">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="P10">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q10">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="R10">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>3.42</v>
+        <v>3.24</v>
       </c>
       <c r="U10">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="V10">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="AA10">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AB10">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="AC10">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AD10">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE10">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AK10">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="O11">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="P11">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="Q11">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R11">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="S11">
         <v>1.19</v>
@@ -2123,10 +2123,10 @@
         <v>3.92</v>
       </c>
       <c r="U11">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="V11">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="W11">
         <v>1.18</v>
@@ -2135,31 +2135,31 @@
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z11">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA11">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AB11">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="AC11">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AD11">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AE11">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF11">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG11">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,61 +2268,61 @@
         <v>1.4</v>
       </c>
       <c r="O12">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P12">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="Q12">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T12">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="U12">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
         <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z12">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA12">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AB12">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC12">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="AD12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AG12">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AK12">
-        <v>2.64</v>
+        <v>2.43</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="O13">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="P13">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q13">
         <v>4.38</v>
@@ -2449,10 +2449,10 @@
         <v>2.18</v>
       </c>
       <c r="U13">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="V13">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W13">
         <v>1.02</v>
@@ -2485,7 +2485,7 @@
         <v>2.2</v>
       </c>
       <c r="AG13">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.43</v>
+        <v>1.98</v>
       </c>
       <c r="O14">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="P14">
-        <v>5.65</v>
+        <v>3.3</v>
       </c>
       <c r="Q14">
-        <v>1.85</v>
+        <v>2.47</v>
       </c>
       <c r="R14">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="S14">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U14">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V14">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W14">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA14">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AB14">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AC14">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD14">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AE14">
+        <v>1.19</v>
+      </c>
+      <c r="AF14">
+        <v>1.43</v>
+      </c>
+      <c r="AG14">
+        <v>2.59</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.25</v>
       </c>
-      <c r="AF14">
-        <v>1.59</v>
-      </c>
-      <c r="AG14">
-        <v>2.19</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.16</v>
-      </c>
       <c r="AK14">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="O15">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="P15">
-        <v>3.25</v>
+        <v>5.61</v>
       </c>
       <c r="Q15">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="R15">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="S15">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T15">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="U15">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V15">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA15">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AB15">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AC15">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD15">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AE15">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF15">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK15">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O16">
         <v>2.8</v>
       </c>
       <c r="P16">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
         <v>3.36</v>
@@ -2959,7 +2959,7 @@
         <v>2.46</v>
       </c>
       <c r="AB16">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC16">
         <v>4.9</v>
@@ -2990,7 +2990,7 @@
         <v>1.33</v>
       </c>
       <c r="AK16">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3092,22 +3092,22 @@
         <v>1.57</v>
       </c>
       <c r="R17">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T17">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U17">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W17">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X17">
         <v>1.02</v>
@@ -3116,28 +3116,28 @@
         <v>1.13</v>
       </c>
       <c r="Z17">
-        <v>4.61</v>
+        <v>3.3</v>
       </c>
       <c r="AA17">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AB17">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC17">
         <v>2.34</v>
       </c>
       <c r="AD17">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE17">
         <v>1.18</v>
       </c>
       <c r="AF17">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AG17">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK17">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="O18">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q18">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R18">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T18">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
         <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="AA18">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AB18">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AC18">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="AD18">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AE18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG18">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK18">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,34 +3406,34 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="O19">
         <v>3.45</v>
       </c>
       <c r="P19">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="Q19">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="R19">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T19">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="U19">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
         <v>1</v>
@@ -3445,25 +3445,25 @@
         <v>3.45</v>
       </c>
       <c r="AA19">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB19">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AC19">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="AD19">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE19">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
         <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="Q20">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="U20">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="V20">
         <v>1.45</v>
       </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z20">
         <v>3.62</v>
       </c>
       <c r="AA20">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB20">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AC20">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AD20">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE20">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P21">
+        <v>3.99</v>
+      </c>
+      <c r="Q21">
+        <v>2.38</v>
+      </c>
+      <c r="R21">
         <v>2.23</v>
       </c>
-      <c r="Q21">
-        <v>3.5</v>
-      </c>
-      <c r="R21">
-        <v>2.2</v>
-      </c>
       <c r="S21">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T21">
-        <v>2.74</v>
+        <v>3.31</v>
       </c>
       <c r="U21">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="V21">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
         <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z21">
-        <v>3.54</v>
+        <v>4.12</v>
       </c>
       <c r="AA21">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AB21">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AC21">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="AD21">
         <v>1.36</v>
       </c>
       <c r="AE21">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF21">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AK21">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,65 +3895,65 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.84</v>
+        <v>2.92</v>
       </c>
       <c r="O22">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P22">
-        <v>3.99</v>
+        <v>2.29</v>
       </c>
       <c r="Q22">
-        <v>2.38</v>
+        <v>3.62</v>
       </c>
       <c r="R22">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="S22">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="U22">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="V22">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
         <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA22">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
+        <v>2</v>
+      </c>
+      <c r="AC22">
+        <v>3.25</v>
+      </c>
+      <c r="AD22">
+        <v>1.29</v>
+      </c>
+      <c r="AE22">
+        <v>1.1</v>
+      </c>
+      <c r="AF22">
+        <v>1.66</v>
+      </c>
+      <c r="AG22">
         <v>2.09</v>
       </c>
-      <c r="AC22">
-        <v>3.05</v>
-      </c>
-      <c r="AD22">
-        <v>1.42</v>
-      </c>
-      <c r="AE22">
-        <v>1.13</v>
-      </c>
-      <c r="AF22">
-        <v>1.7</v>
-      </c>
-      <c r="AG22">
-        <v>2.1</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AK22">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="O24">
-        <v>4.2</v>
+        <v>4.06</v>
       </c>
       <c r="P24">
-        <v>3.88</v>
+        <v>3.72</v>
       </c>
       <c r="Q24">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R24">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S24">
         <v>1.26</v>
       </c>
       <c r="T24">
-        <v>3.35</v>
+        <v>3.84</v>
       </c>
       <c r="U24">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V24">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W24">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="AA24">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB24">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC24">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="AD24">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AE24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF24">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG24">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK24">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="O25">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="P25">
-        <v>1.73</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>4</v>
+        <v>2.07</v>
       </c>
       <c r="R25">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="T25">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U25">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="V25">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA25">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AB25">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="AC25">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="AD25">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AE25">
+        <v>1.3</v>
+      </c>
+      <c r="AF25">
+        <v>1.44</v>
+      </c>
+      <c r="AG25">
+        <v>2.55</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.15</v>
       </c>
-      <c r="AF25">
-        <v>1.62</v>
-      </c>
-      <c r="AG25">
-        <v>2.15</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>2.1</v>
-      </c>
       <c r="AK25">
-        <v>1.14</v>
+        <v>2.36</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.19</v>
+        <v>4.5</v>
       </c>
       <c r="O26">
-        <v>3.46</v>
+        <v>4.15</v>
       </c>
       <c r="P26">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q26">
-        <v>2.59</v>
+        <v>4.5</v>
       </c>
       <c r="R26">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T26">
-        <v>2.82</v>
+        <v>3.36</v>
       </c>
       <c r="U26">
-        <v>2.68</v>
+        <v>2.3</v>
       </c>
       <c r="V26">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
         <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AA26">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AB26">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="AC26">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="AD26">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG26">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK26">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.59</v>
+        <v>2.11</v>
       </c>
       <c r="O27">
-        <v>4.44</v>
+        <v>3.45</v>
       </c>
       <c r="P27">
-        <v>4.7</v>
+        <v>3.22</v>
       </c>
       <c r="Q27">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="R27">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="T27">
-        <v>4.05</v>
+        <v>3.26</v>
       </c>
       <c r="U27">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="V27">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="W27">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
-        <v>6.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA27">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="AB27">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AC27">
-        <v>2.05</v>
+        <v>3.02</v>
       </c>
       <c r="AD27">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AG27">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK27">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>4.45</v>
+        <v>5.15</v>
       </c>
       <c r="O28">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P28">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q28">
-        <v>4.88</v>
+        <v>4.82</v>
       </c>
       <c r="R28">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S28">
         <v>1.26</v>
@@ -4894,13 +4894,13 @@
         <v>3.34</v>
       </c>
       <c r="U28">
-        <v>2.21</v>
+        <v>2.39</v>
       </c>
       <c r="V28">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4918,13 +4918,13 @@
         <v>2.25</v>
       </c>
       <c r="AC28">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="AD28">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE28">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF28">
         <v>1.57</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>2.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5688,25 +5688,25 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O33">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>3.78</v>
+        <v>4.41</v>
       </c>
       <c r="Q33">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="R33">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="S33">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T33">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="U33">
         <v>3.8</v>
@@ -5715,10 +5715,10 @@
         <v>1.22</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X33">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y33">
         <v>1.52</v>
@@ -5730,22 +5730,22 @@
         <v>2.6</v>
       </c>
       <c r="AB33">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AC33">
-        <v>5.33</v>
+        <v>5.39</v>
       </c>
       <c r="AD33">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE33">
         <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AG33">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK33">
         <v>1.86</v>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5851,65 +5851,65 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="P34">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="Q34">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="R34">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="S34">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="T34">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="U34">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="V34">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X34">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y34">
+        <v>1.5</v>
+      </c>
+      <c r="Z34">
+        <v>2.48</v>
+      </c>
+      <c r="AA34">
+        <v>2.75</v>
+      </c>
+      <c r="AB34">
+        <v>1.36</v>
+      </c>
+      <c r="AC34">
+        <v>5.2</v>
+      </c>
+      <c r="AD34">
+        <v>1.13</v>
+      </c>
+      <c r="AE34">
+        <v>1.03</v>
+      </c>
+      <c r="AF34">
+        <v>2.26</v>
+      </c>
+      <c r="AG34">
         <v>1.55</v>
       </c>
-      <c r="Z34">
-        <v>2.42</v>
-      </c>
-      <c r="AA34">
-        <v>2.65</v>
-      </c>
-      <c r="AB34">
-        <v>1.48</v>
-      </c>
-      <c r="AC34">
-        <v>5.25</v>
-      </c>
-      <c r="AD34">
-        <v>1.15</v>
-      </c>
-      <c r="AE34">
-        <v>1.04</v>
-      </c>
-      <c r="AF34">
-        <v>2.18</v>
-      </c>
-      <c r="AG34">
-        <v>1.61</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK34">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-09-08 21:30:00</t>
+          <t>2026-09-08 21:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="O2">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q2">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
         <v>2.15</v>
       </c>
       <c r="S2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T2">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="U2">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
         <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="Z2">
         <v>3.1</v>
       </c>
       <c r="AA2">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB2">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AC2">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AG2">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK2">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q3">
-        <v>3.28</v>
+        <v>4.27</v>
       </c>
       <c r="R3">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="S3">
         <v>1.31</v>
@@ -819,37 +819,37 @@
         <v>3.23</v>
       </c>
       <c r="U3">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="V3">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z3">
-        <v>4.73</v>
+        <v>4.45</v>
       </c>
       <c r="AA3">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB3">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AC3">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AD3">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF3">
         <v>1.52</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
+        <v>1.27</v>
+      </c>
+      <c r="AK3">
         <v>1.29</v>
-      </c>
-      <c r="AK3">
-        <v>1.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="O5">
         <v>3.9</v>
       </c>
       <c r="P5">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q5">
         <v>4.8</v>
       </c>
       <c r="R5">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="S5">
         <v>1.25</v>
@@ -1145,13 +1145,13 @@
         <v>3.38</v>
       </c>
       <c r="U5">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="V5">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="W5">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1163,19 +1163,19 @@
         <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AB5">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC5">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AD5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE5">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
         <v>1.62</v>
@@ -1290,25 +1290,25 @@
         <v>1.44</v>
       </c>
       <c r="O6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P6">
-        <v>4.93</v>
+        <v>5.79</v>
       </c>
       <c r="Q6">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R6">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="S6">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T6">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V6">
         <v>1.67</v>
@@ -1320,10 +1320,10 @@
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="AA6">
         <v>1.44</v>
@@ -1332,19 +1332,19 @@
         <v>2.59</v>
       </c>
       <c r="AC6">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="AD6">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE6">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF6">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG6">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK6">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="O9">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q9">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="R9">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="V9">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
         <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="AA9">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AB9">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AC9">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AD9">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE9">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG9">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="AK9">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P10">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q10">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="R10">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="U10">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="V10">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
         <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>3.94</v>
+        <v>4.5</v>
       </c>
       <c r="AA10">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AB10">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AC10">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AD10">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF10">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG10">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.79</v>
+        <v>4.5</v>
       </c>
       <c r="O24">
-        <v>4.06</v>
+        <v>4.15</v>
       </c>
       <c r="P24">
-        <v>3.72</v>
+        <v>1.67</v>
       </c>
       <c r="Q24">
-        <v>2.28</v>
+        <v>4.5</v>
       </c>
       <c r="R24">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="S24">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="T24">
-        <v>3.84</v>
+        <v>3.36</v>
       </c>
       <c r="U24">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="W24">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z24">
-        <v>5.35</v>
+        <v>4.4</v>
       </c>
       <c r="AA24">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="AB24">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="AC24">
-        <v>2.21</v>
+        <v>2.61</v>
       </c>
       <c r="AD24">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AE24">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AG24">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="AK24">
-        <v>1.95</v>
+        <v>1.14</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
+        <v>2.11</v>
+      </c>
+      <c r="O25">
+        <v>3.45</v>
+      </c>
+      <c r="P25">
+        <v>3.22</v>
+      </c>
+      <c r="Q25">
+        <v>2.8</v>
+      </c>
+      <c r="R25">
+        <v>2.15</v>
+      </c>
+      <c r="S25">
+        <v>1.39</v>
+      </c>
+      <c r="T25">
+        <v>3.26</v>
+      </c>
+      <c r="U25">
+        <v>2.63</v>
+      </c>
+      <c r="V25">
+        <v>1.48</v>
+      </c>
+      <c r="W25">
+        <v>1.09</v>
+      </c>
+      <c r="X25">
+        <v>1.01</v>
+      </c>
+      <c r="Y25">
+        <v>1.27</v>
+      </c>
+      <c r="Z25">
+        <v>3.75</v>
+      </c>
+      <c r="AA25">
+        <v>1.83</v>
+      </c>
+      <c r="AB25">
+        <v>2</v>
+      </c>
+      <c r="AC25">
+        <v>3.02</v>
+      </c>
+      <c r="AD25">
+        <v>1.36</v>
+      </c>
+      <c r="AE25">
+        <v>1.1</v>
+      </c>
+      <c r="AF25">
+        <v>1.63</v>
+      </c>
+      <c r="AG25">
+        <v>2.17</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>1.33</v>
+      </c>
+      <c r="AK25">
         <v>1.6</v>
-      </c>
-      <c r="O25">
-        <v>4.4</v>
-      </c>
-      <c r="P25">
-        <v>5</v>
-      </c>
-      <c r="Q25">
-        <v>2.07</v>
-      </c>
-      <c r="R25">
-        <v>2.41</v>
-      </c>
-      <c r="S25">
-        <v>1.18</v>
-      </c>
-      <c r="T25">
-        <v>3.5</v>
-      </c>
-      <c r="U25">
-        <v>2.13</v>
-      </c>
-      <c r="V25">
-        <v>1.74</v>
-      </c>
-      <c r="W25">
-        <v>1.18</v>
-      </c>
-      <c r="X25">
-        <v>1.03</v>
-      </c>
-      <c r="Y25">
-        <v>1.14</v>
-      </c>
-      <c r="Z25">
-        <v>5.5</v>
-      </c>
-      <c r="AA25">
-        <v>1.43</v>
-      </c>
-      <c r="AB25">
-        <v>2.7</v>
-      </c>
-      <c r="AC25">
-        <v>2</v>
-      </c>
-      <c r="AD25">
-        <v>1.7</v>
-      </c>
-      <c r="AE25">
-        <v>1.3</v>
-      </c>
-      <c r="AF25">
-        <v>1.44</v>
-      </c>
-      <c r="AG25">
-        <v>2.55</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.15</v>
-      </c>
-      <c r="AK25">
-        <v>2.36</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.5</v>
+        <v>1.79</v>
       </c>
       <c r="O26">
-        <v>4.15</v>
+        <v>4.06</v>
       </c>
       <c r="P26">
-        <v>1.67</v>
+        <v>3.72</v>
       </c>
       <c r="Q26">
-        <v>4.5</v>
+        <v>2.28</v>
       </c>
       <c r="R26">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="S26">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="T26">
-        <v>3.36</v>
+        <v>3.84</v>
       </c>
       <c r="U26">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="V26">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="W26">
+        <v>1.15</v>
+      </c>
+      <c r="X26">
+        <v>1.02</v>
+      </c>
+      <c r="Y26">
         <v>1.1</v>
       </c>
-      <c r="X26">
-        <v>1</v>
-      </c>
-      <c r="Y26">
-        <v>1.18</v>
-      </c>
       <c r="Z26">
-        <v>4.4</v>
+        <v>5.35</v>
       </c>
       <c r="AA26">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AB26">
+        <v>2.5</v>
+      </c>
+      <c r="AC26">
         <v>2.21</v>
       </c>
-      <c r="AC26">
-        <v>2.61</v>
-      </c>
       <c r="AD26">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AE26">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>2.1</v>
+        <v>1.26</v>
       </c>
       <c r="AK26">
-        <v>1.14</v>
+        <v>1.95</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.11</v>
+        <v>1.6</v>
       </c>
       <c r="O27">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="P27">
-        <v>3.22</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>2.8</v>
+        <v>2.07</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="S27">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="T27">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="U27">
-        <v>2.63</v>
+        <v>2.13</v>
       </c>
       <c r="V27">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="W27">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA27">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="AB27">
+        <v>2.7</v>
+      </c>
+      <c r="AC27">
         <v>2</v>
       </c>
-      <c r="AC27">
-        <v>3.02</v>
-      </c>
       <c r="AD27">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AF27">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AG27">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AK27">
-        <v>1.6</v>
+        <v>2.36</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="O29">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="P29">
         <v>3.05</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB29">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O31">
         <v>3.1</v>
@@ -5374,52 +5374,52 @@
         <v>2.9</v>
       </c>
       <c r="R31">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="S31">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T31">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U31">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="V31">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W31">
         <v>1.04</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Z31">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA31">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AB31">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AC31">
-        <v>2.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD31">
         <v>1.22</v>
       </c>
       <c r="AE31">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG31">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="O32">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="Q32">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="R32">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="S32">
+        <v>1.34</v>
+      </c>
+      <c r="T32">
+        <v>2.7</v>
+      </c>
+      <c r="U32">
+        <v>2.74</v>
+      </c>
+      <c r="V32">
+        <v>1.37</v>
+      </c>
+      <c r="W32">
+        <v>1.07</v>
+      </c>
+      <c r="X32">
+        <v>1.03</v>
+      </c>
+      <c r="Y32">
+        <v>1.23</v>
+      </c>
+      <c r="Z32">
+        <v>3.8</v>
+      </c>
+      <c r="AA32">
+        <v>1.9</v>
+      </c>
+      <c r="AB32">
+        <v>1.88</v>
+      </c>
+      <c r="AC32">
+        <v>3.14</v>
+      </c>
+      <c r="AD32">
         <v>1.3</v>
-      </c>
-      <c r="T32">
-        <v>3.2</v>
-      </c>
-      <c r="U32">
-        <v>2.66</v>
-      </c>
-      <c r="V32">
-        <v>1.39</v>
-      </c>
-      <c r="W32">
-        <v>1.1</v>
-      </c>
-      <c r="X32">
-        <v>1</v>
-      </c>
-      <c r="Y32">
-        <v>1.22</v>
-      </c>
-      <c r="Z32">
-        <v>3.5</v>
-      </c>
-      <c r="AA32">
-        <v>1.83</v>
-      </c>
-      <c r="AB32">
-        <v>1.87</v>
-      </c>
-      <c r="AC32">
-        <v>2.63</v>
-      </c>
-      <c r="AD32">
-        <v>1.28</v>
       </c>
       <c r="AE32">
         <v>1.07</v>
       </c>
       <c r="AF32">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AL32">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43", "70"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -787,14 +787,14 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,7 +859,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,36 +938,36 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
         <v>1.85</v>
       </c>
       <c r="O4">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="P4">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1000,7 +1000,7 @@
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB4">
         <v>2.25</v>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63", "76", "90"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "49", "58"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O11">
+        <v>4.2</v>
+      </c>
+      <c r="P11">
+        <v>4.7</v>
+      </c>
+      <c r="Q11">
+        <v>1.97</v>
+      </c>
+      <c r="R11">
+        <v>2.55</v>
+      </c>
+      <c r="S11">
+        <v>1.17</v>
+      </c>
+      <c r="T11">
         <v>4.5</v>
       </c>
-      <c r="P11">
-        <v>5.25</v>
-      </c>
-      <c r="Q11">
-        <v>1.98</v>
-      </c>
-      <c r="R11">
-        <v>2.7</v>
-      </c>
-      <c r="S11">
-        <v>1.19</v>
-      </c>
-      <c r="T11">
-        <v>3.92</v>
-      </c>
       <c r="U11">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="V11">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="W11">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA11">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB11">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC11">
-        <v>1.96</v>
+        <v>2.19</v>
       </c>
       <c r="AD11">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AE11">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AF11">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG11">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AL11">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -1453,61 +1453,61 @@
         <v>1.95</v>
       </c>
       <c r="O7">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="P7">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Q7">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="R7">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W7">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="AA7">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB7">
         <v>2.28</v>
       </c>
       <c r="AC7">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AD7">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE7">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG7">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK7">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
+        <v>3.73</v>
+      </c>
+      <c r="O8">
+        <v>3.4</v>
+      </c>
+      <c r="P8">
+        <v>1.93</v>
+      </c>
+      <c r="Q8">
+        <v>4.4</v>
+      </c>
+      <c r="R8">
+        <v>2.05</v>
+      </c>
+      <c r="S8">
+        <v>1.39</v>
+      </c>
+      <c r="T8">
+        <v>2.66</v>
+      </c>
+      <c r="U8">
+        <v>2.77</v>
+      </c>
+      <c r="V8">
+        <v>1.36</v>
+      </c>
+      <c r="W8">
+        <v>1.05</v>
+      </c>
+      <c r="X8">
+        <v>1.02</v>
+      </c>
+      <c r="Y8">
+        <v>1.25</v>
+      </c>
+      <c r="Z8">
+        <v>3.33</v>
+      </c>
+      <c r="AA8">
+        <v>1.95</v>
+      </c>
+      <c r="AB8">
+        <v>1.8</v>
+      </c>
+      <c r="AC8">
         <v>3.2</v>
       </c>
-      <c r="O8">
-        <v>3.25</v>
-      </c>
-      <c r="P8">
-        <v>1.95</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>1.85</v>
-      </c>
-      <c r="AB8">
-        <v>1.95</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="O12">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P12">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="Q12">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="R12">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T12">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>2.97</v>
+        <v>3.45</v>
       </c>
       <c r="AA12">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="AB12">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>3.79</v>
+        <v>3.14</v>
       </c>
       <c r="AD12">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
+        <v>1.08</v>
+      </c>
+      <c r="AF12">
+        <v>1.94</v>
+      </c>
+      <c r="AG12">
+        <v>1.73</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.03</v>
       </c>
-      <c r="AF12">
-        <v>2.38</v>
-      </c>
-      <c r="AG12">
-        <v>1.52</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.07</v>
-      </c>
       <c r="AK12">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="O13">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="P13">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q13">
-        <v>4.38</v>
+        <v>3.85</v>
       </c>
       <c r="R13">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="S13">
         <v>1.57</v>
       </c>
       <c r="T13">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="U13">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="V13">
         <v>1.22</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
         <v>1.1</v>
       </c>
       <c r="Y13">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z13">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AA13">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="AB13">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AD13">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AG13">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK13">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O14">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
         <v>3.3</v>
       </c>
       <c r="Q14">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="R14">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T14">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
         <v>2.15</v>
       </c>
       <c r="V14">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA14">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AB14">
         <v>2.38</v>
       </c>
       <c r="AC14">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AD14">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AE14">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AG14">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK14">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="O15">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="P15">
-        <v>5.61</v>
+        <v>6.7</v>
       </c>
       <c r="Q15">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R15">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="S15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="U15">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V15">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W15">
         <v>1.14</v>
@@ -2787,22 +2787,22 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z15">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA15">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB15">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AC15">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD15">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE15">
         <v>1.25</v>
@@ -2811,7 +2811,7 @@
         <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK15">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-09-08.xlsx
+++ b/jogos_2026-09-08.xlsx
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -1120,14 +1120,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>4.65</v>
+        <v>4.85</v>
       </c>
       <c r="O5">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
         <v>1.55</v>
@@ -1136,95 +1136,95 @@
         <v>4.8</v>
       </c>
       <c r="R5">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="S5">
         <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="U5">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
         <v>1.2</v>
       </c>
       <c r="Z5">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA5">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AB5">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AC5">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="AD5">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF5">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "28"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "43"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.16</v>
+        <v>2.3</v>
       </c>
       <c r="AK5">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,100 +1264,100 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
         <v>1.44</v>
       </c>
       <c r="O6">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P6">
-        <v>5.79</v>
+        <v>5.25</v>
       </c>
       <c r="Q6">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="R6">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="S6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>3.84</v>
       </c>
       <c r="U6">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V6">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W6">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
+        <v>1.08</v>
+      </c>
+      <c r="Z6">
+        <v>6</v>
+      </c>
+      <c r="AA6">
+        <v>1.35</v>
+      </c>
+      <c r="AB6">
+        <v>2.62</v>
+      </c>
+      <c r="AC6">
+        <v>2.03</v>
+      </c>
+      <c r="AD6">
+        <v>1.7</v>
+      </c>
+      <c r="AE6">
+        <v>1.26</v>
+      </c>
+      <c r="AF6">
+        <v>1.53</v>
+      </c>
+      <c r="AG6">
+        <v>2.3</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>["76"]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>["19", "30"]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.07</v>
-      </c>
-      <c r="Z6">
-        <v>3.75</v>
-      </c>
-      <c r="AA6">
-        <v>1.44</v>
-      </c>
-      <c r="AB6">
-        <v>2.59</v>
-      </c>
-      <c r="AC6">
-        <v>2.11</v>
-      </c>
-      <c r="AD6">
-        <v>1.68</v>
-      </c>
-      <c r="AE6">
-        <v>1.2</v>
-      </c>
-      <c r="AF6">
-        <v>1.55</v>
-      </c>
-      <c r="AG6">
-        <v>2.27</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.13</v>
       </c>
       <c r="AK6">
         <v>2.63</v>
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,130 +1753,130 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="O9">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="P9">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q9">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R9">
         <v>2.25</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T9">
-        <v>3.24</v>
+        <v>3.36</v>
       </c>
       <c r="U9">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z9">
-        <v>3.94</v>
+        <v>4.3</v>
       </c>
       <c r="AA9">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AB9">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AC9">
-        <v>2.59</v>
+        <v>2.44</v>
       </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE9">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
+        <v>1.55</v>
+      </c>
+      <c r="AG9">
+        <v>2.45</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>["19", "61"]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>["11", "22", "43"]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.32</v>
+      </c>
+      <c r="AK9">
         <v>1.57</v>
       </c>
-      <c r="AG9">
-        <v>2.3</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.52</v>
-      </c>
-      <c r="AK9">
-        <v>1.44</v>
-      </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1935,111 +1935,111 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="O10">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P10">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q10">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="R10">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
         <v>1.55</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z10">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA10">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AB10">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="AC10">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="AD10">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AE10">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF10">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AG10">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
+          <t>["21"]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O11">
         <v>4.2</v>
       </c>
       <c r="P11">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q11">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R11">
         <v>2.55</v>
       </c>
       <c r="S11">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T11">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U11">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="V11">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W11">
         <v>1.2</v>
@@ -2135,31 +2135,31 @@
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z11">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA11">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB11">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AC11">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AD11">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF11">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG11">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK11">
         <v>2.22</v>
@@ -2242,26 +2242,26 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "87"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
+        <v>1.4</v>
+      </c>
+      <c r="O14">
+        <v>5.1</v>
+      </c>
+      <c r="P14">
+        <v>6.7</v>
+      </c>
+      <c r="Q14">
+        <v>1.83</v>
+      </c>
+      <c r="R14">
+        <v>2.55</v>
+      </c>
+      <c r="S14">
+        <v>1.2</v>
+      </c>
+      <c r="T14">
+        <v>3.68</v>
+      </c>
+      <c r="U14">
         <v>2.05</v>
       </c>
-      <c r="O14">
-        <v>3.6</v>
-      </c>
-      <c r="P14">
-        <v>3.3</v>
-      </c>
-      <c r="Q14">
-        <v>2.59</v>
-      </c>
-      <c r="R14">
-        <v>2.41</v>
-      </c>
-      <c r="S14">
-        <v>1.27</v>
-      </c>
-      <c r="T14">
-        <v>3.25</v>
-      </c>
-      <c r="U14">
+      <c r="V14">
+        <v>1.7</v>
+      </c>
+      <c r="W14">
+        <v>1.14</v>
+      </c>
+      <c r="X14">
+        <v>1.02</v>
+      </c>
+      <c r="Y14">
+        <v>1.09</v>
+      </c>
+      <c r="Z14">
+        <v>5.75</v>
+      </c>
+      <c r="AA14">
+        <v>1.45</v>
+      </c>
+      <c r="AB14">
+        <v>2.7</v>
+      </c>
+      <c r="AC14">
         <v>2.15</v>
       </c>
-      <c r="V14">
-        <v>1.52</v>
-      </c>
-      <c r="W14">
-        <v>1.08</v>
-      </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>1.18</v>
-      </c>
-      <c r="Z14">
-        <v>5.1</v>
-      </c>
-      <c r="AA14">
-        <v>1.53</v>
-      </c>
-      <c r="AB14">
-        <v>2.38</v>
-      </c>
-      <c r="AC14">
-        <v>2.6</v>
-      </c>
       <c r="AD14">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF14">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG14">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AK14">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="O15">
+        <v>3.6</v>
+      </c>
+      <c r="P15">
+        <v>3.3</v>
+      </c>
+      <c r="Q15">
+        <v>2.59</v>
+      </c>
+      <c r="R15">
+        <v>2.41</v>
+      </c>
+      <c r="S15">
+        <v>1.27</v>
+      </c>
+      <c r="T15">
+        <v>3.25</v>
+      </c>
+      <c r="U15">
+        <v>2.15</v>
+      </c>
+      <c r="V15">
+        <v>1.52</v>
+      </c>
+      <c r="W15">
+        <v>1.08</v>
+      </c>
+      <c r="X15">
+        <v>1.01</v>
+      </c>
+      <c r="Y15">
+        <v>1.18</v>
+      </c>
+      <c r="Z15">
         <v>5.1</v>
       </c>
-      <c r="P15">
-        <v>6.7</v>
-      </c>
-      <c r="Q15">
-        <v>1.83</v>
-      </c>
-      <c r="R15">
-        <v>2.55</v>
-      </c>
-      <c r="S15">
-        <v>1.2</v>
-      </c>
-      <c r="T15">
-        <v>3.68</v>
-      </c>
-      <c r="U15">
-        <v>2.05</v>
-      </c>
-      <c r="V15">
-        <v>1.7</v>
-      </c>
-      <c r="W15">
-        <v>1.14</v>
-      </c>
-      <c r="X15">
-        <v>1.02</v>
-      </c>
-      <c r="Y15">
-        <v>1.09</v>
-      </c>
-      <c r="Z15">
-        <v>5.75</v>
-      </c>
       <c r="AA15">
+        <v>1.53</v>
+      </c>
+      <c r="AB15">
+        <v>2.38</v>
+      </c>
+      <c r="AC15">
+        <v>2.6</v>
+      </c>
+      <c r="AD15">
         <v>1.45</v>
       </c>
-      <c r="AB15">
-        <v>2.7</v>
-      </c>
-      <c r="AC15">
-        <v>2.15</v>
-      </c>
-      <c r="AD15">
-        <v>1.67</v>
-      </c>
       <c r="AE15">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG15">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2913,81 +2913,81 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O16">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q16">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="R16">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="S16">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="T16">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="U16">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="V16">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="W16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="Z16">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="AA16">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="AB16">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC16">
-        <v>4.9</v>
+        <v>3.98</v>
       </c>
       <c r="AD16">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE16">
         <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
+          <t>["37"]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ16">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AK16">
         <v>1.41</v>
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="O17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q17">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="R17">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="S17">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V17">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z17">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="AA17">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB17">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC17">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AD17">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE17">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AG17">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK17">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q18">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="R18">
+        <v>2.31</v>
+      </c>
+      <c r="S18">
+        <v>1.3</v>
+      </c>
+      <c r="T18">
+        <v>3.35</v>
+      </c>
+      <c r="U18">
         <v>2.3</v>
       </c>
-      <c r="S18">
-        <v>1.29</v>
-      </c>
-      <c r="T18">
-        <v>3.5</v>
-      </c>
-      <c r="U18">
-        <v>2.2</v>
-      </c>
       <c r="V18">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
         <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AA18">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AB18">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AC18">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AD18">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE18">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF18">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AG18">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,55 +3406,55 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O19">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>3.02</v>
+        <v>3.61</v>
       </c>
       <c r="Q19">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R19">
         <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U19">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V19">
         <v>1.42</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>1.28</v>
       </c>
       <c r="Z19">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AA19">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB19">
         <v>1.83</v>
       </c>
       <c r="AC19">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AD19">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
         <v>1.07</v>
@@ -3463,7 +3463,7 @@
         <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="Q20">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R20">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T20">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U20">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="V20">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
         <v>1.07</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="AA20">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AB20">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AC20">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD20">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE20">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG20">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK20">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,61 +3732,61 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="O21">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P21">
-        <v>3.99</v>
+        <v>3.9</v>
       </c>
       <c r="Q21">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R21">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S21">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T21">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="U21">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z21">
-        <v>4.12</v>
+        <v>3.9</v>
       </c>
       <c r="AA21">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB21">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AC21">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AD21">
         <v>1.36</v>
       </c>
       <c r="AE21">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AG21">
         <v>2.07</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,28 +3895,28 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O22">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P22">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="Q22">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="R22">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T22">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="V22">
         <v>1.44</v>
@@ -3925,7 +3925,7 @@
         <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y22">
         <v>1.22</v>
@@ -3934,7 +3934,7 @@
         <v>4.1</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AB22">
         <v>2</v>
@@ -3943,16 +3943,16 @@
         <v>3.25</v>
       </c>
       <c r="AD22">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE22">
         <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG22">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,55 +4221,55 @@
         </is>
       </c>
       <c r="N24">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="O24">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="P24">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Q24">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="R24">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S24">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="U24">
         <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z24">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="AA24">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB24">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AC24">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="AD24">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE24">
         <v>1.14</v>
@@ -4278,7 +4278,7 @@
         <v>1.65</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AK24">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="O25">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="Q25">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="R25">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
-        <v>3.26</v>
+        <v>3.02</v>
       </c>
       <c r="U25">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V25">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W25">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z25">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA25">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB25">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC25">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="AD25">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE25">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="O26">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="P26">
-        <v>3.72</v>
+        <v>3.95</v>
       </c>
       <c r="Q26">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="R26">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S26">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T26">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="U26">
         <v>2.16</v>
       </c>
       <c r="V26">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="W26">
         <v>1.15</v>
@@ -4580,31 +4580,31 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z26">
-        <v>5.35</v>
+        <v>6</v>
       </c>
       <c r="AA26">
         <v>1.45</v>
       </c>
       <c r="AB26">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AC26">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AD26">
         <v>1.62</v>
       </c>
       <c r="AE26">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF26">
         <v>1.45</v>
       </c>
       <c r="AG26">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="O27">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="P27">
         <v>5</v>
       </c>
       <c r="Q27">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="R27">
-        <v>2.41</v>
+        <v>2.54</v>
       </c>
       <c r="S27">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T27">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="U27">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="V27">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="W27">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X27">
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA27">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB27">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC27">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AD27">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AE27">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF27">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG27">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK27">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,61 +4873,61 @@
         </is>
       </c>
       <c r="N28">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="P28">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q28">
-        <v>4.82</v>
+        <v>5.18</v>
       </c>
       <c r="R28">
-        <v>2.41</v>
+        <v>2.64</v>
       </c>
       <c r="S28">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T28">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="U28">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="V28">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W28">
         <v>1.13</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
         <v>1.14</v>
       </c>
       <c r="Z28">
-        <v>4.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA28">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AB28">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC28">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AD28">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE28">
         <v>1.2</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG28">
         <v>2.25</v>
@@ -4946,7 +4946,7 @@
         <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O33">
         <v>3.1</v>
@@ -5697,19 +5697,19 @@
         <v>4.41</v>
       </c>
       <c r="Q33">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="R33">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="S33">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="T33">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="U33">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="V33">
         <v>1.22</v>
@@ -5718,34 +5718,34 @@
         <v>1.02</v>
       </c>
       <c r="X33">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Y33">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Z33">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AA33">
         <v>2.6</v>
       </c>
       <c r="AB33">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AC33">
-        <v>5.39</v>
+        <v>5.61</v>
       </c>
       <c r="AD33">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE33">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF33">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AG33">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AK33">
         <v>1.86</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O34">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P34">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q34">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="R34">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="S34">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="T34">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="U34">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="V34">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W34">
+        <v>1.03</v>
+      </c>
+      <c r="X34">
+        <v>1.08</v>
+      </c>
+      <c r="Y34">
+        <v>1.57</v>
+      </c>
+      <c r="Z34">
+        <v>2.43</v>
+      </c>
+      <c r="AA34">
+        <v>2.62</v>
+      </c>
+      <c r="AB34">
+        <v>1.43</v>
+      </c>
+      <c r="AC34">
+        <v>5.62</v>
+      </c>
+      <c r="AD34">
+        <v>1.15</v>
+      </c>
+      <c r="AE34">
         <v>1.01</v>
       </c>
-      <c r="X34">
-        <v>1.1</v>
-      </c>
-      <c r="Y34">
-        <v>1.5</v>
-      </c>
-      <c r="Z34">
-        <v>2.48</v>
-      </c>
-      <c r="AA34">
-        <v>2.75</v>
-      </c>
-      <c r="AB34">
-        <v>1.36</v>
-      </c>
-      <c r="AC34">
-        <v>5.2</v>
-      </c>
-      <c r="AD34">
-        <v>1.13</v>
-      </c>
-      <c r="AE34">
-        <v>1.03</v>
-      </c>
       <c r="AF34">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AG34">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AL34">
         <v>0</v>
